--- a/Wy_Ed_Jobs/hedata.xlsx
+++ b/Wy_Ed_Jobs/hedata.xlsx
@@ -1986,7 +1986,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Construction Instructor</t>
+          <t>Part-time Faculty Pool - English Instructor</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4099</t>
+          <t>https://jobs.sheridan.edu/postings/2725</t>
         </is>
       </c>
       <c r="F55" s="2">
@@ -2016,7 +2016,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - English Instructor</t>
+          <t>Hospitality Faculty Coordinator</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/2725</t>
+          <t>https://jobs.sheridan.edu/postings/4660</t>
         </is>
       </c>
       <c r="F56" s="2">
@@ -2046,7 +2046,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Hospitality Faculty Coordinator</t>
+          <t>Part-time Faculty Pool - Construction Instructor</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4660</t>
+          <t>https://jobs.sheridan.edu/postings/4099</t>
         </is>
       </c>
       <c r="F57" s="2">
@@ -2376,7 +2376,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Residential Life Coordinator</t>
+          <t>Part-time Faculty Pool - Online Criminal Justice Instructor</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4568</t>
+          <t>https://jobs.sheridan.edu/postings/4086</t>
         </is>
       </c>
       <c r="F68" s="2">
@@ -2406,7 +2406,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Online Criminal Justice Instructor</t>
+          <t>Residential Life Coordinator</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4086</t>
+          <t>https://jobs.sheridan.edu/postings/4568</t>
         </is>
       </c>
       <c r="F69" s="2">
@@ -2796,7 +2796,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Math Instructor</t>
+          <t>(Student Position) WCA Gallery Assistant</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3938</t>
+          <t>https://jobs.sheridan.edu/postings/4507</t>
         </is>
       </c>
       <c r="F82" s="2">
@@ -2826,7 +2826,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>(Student Position) WCA Gallery Assistant</t>
+          <t>Part-time Faculty Pool - Math Instructor</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4507</t>
+          <t>https://jobs.sheridan.edu/postings/3938</t>
         </is>
       </c>
       <c r="F83" s="2">
@@ -2976,7 +2976,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - History Instructor</t>
+          <t>Administrative &amp; Work Based Learning Coordinator</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4098</t>
+          <t>https://jobs.sheridan.edu/postings/4656</t>
         </is>
       </c>
       <c r="F88" s="2">
@@ -3006,7 +3006,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Administrative &amp; Work Based Learning Coordinator</t>
+          <t>Part-time Faculty Pool - History Instructor</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4656</t>
+          <t>https://jobs.sheridan.edu/postings/4098</t>
         </is>
       </c>
       <c r="F89" s="2">
@@ -3096,7 +3096,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Hospitality/Tourism</t>
+          <t>Part-time Faculty Pool - Dental Hygiene Instructor</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4101</t>
+          <t>https://jobs.sheridan.edu/postings/2847</t>
         </is>
       </c>
       <c r="F92" s="2">
@@ -3126,7 +3126,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Dental Hygiene Instructor</t>
+          <t>Custodial Manager</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/2847</t>
+          <t>https://jobs.sheridan.edu/postings/4665</t>
         </is>
       </c>
       <c r="F93" s="2">
@@ -3156,7 +3156,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Custodial Manager</t>
+          <t>Part-time Faculty Pool - Hospitality/Tourism</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4665</t>
+          <t>https://jobs.sheridan.edu/postings/4101</t>
         </is>
       </c>
       <c r="F94" s="2">
@@ -3336,7 +3336,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>(Student Position) Box Office Assistant</t>
+          <t>Part-time Faculty Pool - Human Services Instructor</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4560</t>
+          <t>https://jobs.sheridan.edu/postings/4085</t>
         </is>
       </c>
       <c r="F100" s="2">
@@ -3366,7 +3366,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Human Services Instructor</t>
+          <t>(Student Position) Box Office Assistant</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4085</t>
+          <t>https://jobs.sheridan.edu/postings/4560</t>
         </is>
       </c>
       <c r="F101" s="2">
@@ -3756,7 +3756,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Agriculture Instructor</t>
+          <t>(Student Position) Information Technology (IT) Night Helpdesk</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3852</t>
+          <t>https://jobs.sheridan.edu/postings/4502</t>
         </is>
       </c>
       <c r="F114" s="2">
@@ -3786,7 +3786,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>(Student Position) Information Technology (IT) Night Helpdesk</t>
+          <t>Part-time Faculty Pool - Agriculture Instructor</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4502</t>
+          <t>https://jobs.sheridan.edu/postings/3852</t>
         </is>
       </c>
       <c r="F115" s="2">

--- a/Wy_Ed_Jobs/hedata.xlsx
+++ b/Wy_Ed_Jobs/hedata.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F347"/>
+  <dimension ref="A1:F348"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
@@ -1746,7 +1746,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>(Student Position) Sports and Recreation Assistant</t>
+          <t>Part-time Faculty Pool - Spanish Instructor</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4647</t>
+          <t>https://jobs.sheridan.edu/postings/4095</t>
         </is>
       </c>
       <c r="F47" s="2">
@@ -1776,7 +1776,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Spanish Instructor</t>
+          <t>(Student Position) Sports and Recreation Assistant</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4095</t>
+          <t>https://jobs.sheridan.edu/postings/4647</t>
         </is>
       </c>
       <c r="F48" s="2">
@@ -1866,7 +1866,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>(Student Position) Outdoor Recreation Assistant</t>
+          <t>Part-time Faculty Pool - Composites Manufacturing</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4651</t>
+          <t>https://jobs.sheridan.edu/postings/4097</t>
         </is>
       </c>
       <c r="F51" s="2">
@@ -1896,7 +1896,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Composites Manufacturing</t>
+          <t>(Student Position) Outdoor Recreation Assistant</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4097</t>
+          <t>https://jobs.sheridan.edu/postings/4651</t>
         </is>
       </c>
       <c r="F52" s="2">
@@ -1986,7 +1986,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - English Instructor</t>
+          <t>Part-time Faculty Pool - Construction Instructor</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/2725</t>
+          <t>https://jobs.sheridan.edu/postings/4099</t>
         </is>
       </c>
       <c r="F55" s="2">
@@ -2016,7 +2016,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Hospitality Faculty Coordinator</t>
+          <t>Part-time Faculty Pool - English Instructor</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4660</t>
+          <t>https://jobs.sheridan.edu/postings/2725</t>
         </is>
       </c>
       <c r="F56" s="2">
@@ -2046,7 +2046,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Construction Instructor</t>
+          <t>Hospitality Faculty Coordinator</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4099</t>
+          <t>https://jobs.sheridan.edu/postings/4660</t>
         </is>
       </c>
       <c r="F57" s="2">
@@ -2076,7 +2076,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Acting II Instructor</t>
+          <t>(Student Position) Writing Center Peer Consultant</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3985</t>
+          <t>https://jobs.sheridan.edu/postings/4521</t>
         </is>
       </c>
       <c r="F58" s="2">
@@ -2106,7 +2106,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>(Student Position) Writing Center Peer Consultant</t>
+          <t>Part-time Faculty Pool - Acting II Instructor</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4521</t>
+          <t>https://jobs.sheridan.edu/postings/3985</t>
         </is>
       </c>
       <c r="F59" s="2">
@@ -2226,7 +2226,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Community Interest (CI) Johnson County</t>
+          <t>(Student Position )Library Helpdesk</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4084</t>
+          <t>https://jobs.sheridan.edu/postings/4525</t>
         </is>
       </c>
       <c r="F63" s="2">
@@ -2256,7 +2256,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>(Student Position )Library Helpdesk</t>
+          <t>Part-time Faculty Pool - Community Interest (CI) Johnson County</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4525</t>
+          <t>https://jobs.sheridan.edu/postings/4084</t>
         </is>
       </c>
       <c r="F64" s="2">
@@ -2286,7 +2286,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Electrical Apprenticeship Instructor</t>
+          <t>(Student Position) Youth Soccer Referee - YMCA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4197</t>
+          <t>https://jobs.sheridan.edu/postings/4681</t>
         </is>
       </c>
       <c r="F65" s="2">
@@ -2316,7 +2316,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Astronomy Instructor</t>
+          <t>Part-time Faculty Pool - Electrical Apprenticeship Instructor</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2022-08-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3311</t>
+          <t>https://jobs.sheridan.edu/postings/4197</t>
         </is>
       </c>
       <c r="F66" s="2">
@@ -2346,7 +2346,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>(Student Position) Youth Soccer Referee - YMCA</t>
+          <t>Part-time Faculty Pool - Astronomy Instructor</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2022-08-03</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4681</t>
+          <t>https://jobs.sheridan.edu/postings/3311</t>
         </is>
       </c>
       <c r="F67" s="2">
@@ -2376,7 +2376,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Online Criminal Justice Instructor</t>
+          <t>Residential Life Coordinator</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4086</t>
+          <t>https://jobs.sheridan.edu/postings/4568</t>
         </is>
       </c>
       <c r="F68" s="2">
@@ -2406,7 +2406,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Residential Life Coordinator</t>
+          <t>Part-time Faculty Pool - Online Criminal Justice Instructor</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4568</t>
+          <t>https://jobs.sheridan.edu/postings/4086</t>
         </is>
       </c>
       <c r="F69" s="2">
@@ -2556,7 +2556,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Computer Science or Information Technology Instructor</t>
+          <t>Part-time Faculty Pool - Adobe Creative Cloud Instructor</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4489</t>
+          <t>https://jobs.sheridan.edu/postings/3759</t>
         </is>
       </c>
       <c r="F74" s="2">
@@ -2586,7 +2586,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Adobe Creative Cloud Instructor</t>
+          <t>Part-time Faculty Pool - Computer Science or Information Technology Instructor</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3759</t>
+          <t>https://jobs.sheridan.edu/postings/4489</t>
         </is>
       </c>
       <c r="F75" s="2">
@@ -2676,7 +2676,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>(Student Position) Enrollment Services Assistant</t>
+          <t>Part-time Faculty Pool - Accounting Instructor</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4500</t>
+          <t>https://jobs.sheridan.edu/postings/3763</t>
         </is>
       </c>
       <c r="F78" s="2">
@@ -2706,7 +2706,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Accounting Instructor</t>
+          <t>(Student Position) Enrollment Services Assistant</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3763</t>
+          <t>https://jobs.sheridan.edu/postings/4500</t>
         </is>
       </c>
       <c r="F79" s="2">
@@ -2736,7 +2736,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>(Student Position) General’s Pantry Assistant</t>
+          <t>Part-time Faculty Pool - Geology Instructor</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4645</t>
+          <t>https://jobs.sheridan.edu/postings/4094</t>
         </is>
       </c>
       <c r="F80" s="2">
@@ -2766,7 +2766,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Geology Instructor</t>
+          <t>(Student Position) General’s Pantry Assistant</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4094</t>
+          <t>https://jobs.sheridan.edu/postings/4645</t>
         </is>
       </c>
       <c r="F81" s="2">
@@ -2796,7 +2796,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>(Student Position) WCA Gallery Assistant</t>
+          <t>Part-time Faculty Pool - Math Instructor</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4507</t>
+          <t>https://jobs.sheridan.edu/postings/3938</t>
         </is>
       </c>
       <c r="F82" s="2">
@@ -2826,7 +2826,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Math Instructor</t>
+          <t>(Student Position) WCA Gallery Assistant</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3938</t>
+          <t>https://jobs.sheridan.edu/postings/4507</t>
         </is>
       </c>
       <c r="F83" s="2">
@@ -2856,7 +2856,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>(Student Position) Sports &amp; Recreation Manager</t>
+          <t>Part-time Faculty Pool - Communications Instructor</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4649</t>
+          <t>https://jobs.sheridan.edu/postings/4096</t>
         </is>
       </c>
       <c r="F84" s="2">
@@ -2886,7 +2886,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Communications Instructor</t>
+          <t>(Student Position) Sports &amp; Recreation Manager</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4096</t>
+          <t>https://jobs.sheridan.edu/postings/4649</t>
         </is>
       </c>
       <c r="F85" s="2">
@@ -2976,7 +2976,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Administrative &amp; Work Based Learning Coordinator</t>
+          <t>Part-time Faculty Pool - History Instructor</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4656</t>
+          <t>https://jobs.sheridan.edu/postings/4098</t>
         </is>
       </c>
       <c r="F88" s="2">
@@ -3006,7 +3006,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - History Instructor</t>
+          <t>Administrative &amp; Work Based Learning Coordinator</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4098</t>
+          <t>https://jobs.sheridan.edu/postings/4656</t>
         </is>
       </c>
       <c r="F89" s="2">
@@ -3036,7 +3036,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Health and Human Performance Instructor</t>
+          <t>(Student Position) Financial Aid Office Assistant</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3983</t>
+          <t>https://jobs.sheridan.edu/postings/4519</t>
         </is>
       </c>
       <c r="F90" s="2">
@@ -3066,7 +3066,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>(Student Position) Financial Aid Office Assistant</t>
+          <t>Part-time Faculty Pool - Health and Human Performance Instructor</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4519</t>
+          <t>https://jobs.sheridan.edu/postings/3983</t>
         </is>
       </c>
       <c r="F91" s="2">
@@ -3096,7 +3096,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Dental Hygiene Instructor</t>
+          <t>Part-time Faculty Pool - Hospitality/Tourism</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/2847</t>
+          <t>https://jobs.sheridan.edu/postings/4101</t>
         </is>
       </c>
       <c r="F92" s="2">
@@ -3126,7 +3126,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Custodial Manager</t>
+          <t>Part-time Faculty Pool - Dental Hygiene Instructor</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4665</t>
+          <t>https://jobs.sheridan.edu/postings/2847</t>
         </is>
       </c>
       <c r="F93" s="2">
@@ -3156,7 +3156,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Hospitality/Tourism</t>
+          <t>Custodial Manager</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4101</t>
+          <t>https://jobs.sheridan.edu/postings/4665</t>
         </is>
       </c>
       <c r="F94" s="2">
@@ -3186,7 +3186,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Massage Therapy Instructor</t>
+          <t>(Student Position) Peer Tutor</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4048</t>
+          <t>https://jobs.sheridan.edu/postings/4523</t>
         </is>
       </c>
       <c r="F95" s="2">
@@ -3216,7 +3216,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>(Student Position) Peer Tutor</t>
+          <t>Part-time Faculty Pool - Massage Therapy Instructor</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4523</t>
+          <t>https://jobs.sheridan.edu/postings/4048</t>
         </is>
       </c>
       <c r="F96" s="2">
@@ -3336,7 +3336,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Human Services Instructor</t>
+          <t>(Student Position) Box Office Assistant</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4085</t>
+          <t>https://jobs.sheridan.edu/postings/4560</t>
         </is>
       </c>
       <c r="F100" s="2">
@@ -3366,7 +3366,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>(Student Position) Box Office Assistant</t>
+          <t>Part-time Faculty Pool - Human Services Instructor</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4560</t>
+          <t>https://jobs.sheridan.edu/postings/4085</t>
         </is>
       </c>
       <c r="F101" s="2">
@@ -3396,7 +3396,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Welding Instructor</t>
+          <t>Vice President of Academic Affairs</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4470</t>
+          <t>https://jobs.sheridan.edu/postings/4682</t>
         </is>
       </c>
       <c r="F102" s="2">
@@ -3426,7 +3426,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Nursing Instructor</t>
+          <t>Part-time Faculty Pool - Welding Instructor</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2022-08-16</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3326</t>
+          <t>https://jobs.sheridan.edu/postings/4470</t>
         </is>
       </c>
       <c r="F103" s="2">
@@ -3456,7 +3456,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>(Student Position) 3D Technician</t>
+          <t>Part-time Faculty Pool - Nursing Instructor</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2022-08-16</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4580</t>
+          <t>https://jobs.sheridan.edu/postings/3326</t>
         </is>
       </c>
       <c r="F104" s="2">
@@ -3486,7 +3486,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Psychology Instructor</t>
+          <t>(Student Position) 3D Technician</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4087</t>
+          <t>https://jobs.sheridan.edu/postings/4580</t>
         </is>
       </c>
       <c r="F105" s="2">
@@ -3516,7 +3516,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Commercial Motor Vehicle (CMV) Driver Training Instructor</t>
+          <t>Part-time Faculty Pool - Psychology Instructor</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4487</t>
+          <t>https://jobs.sheridan.edu/postings/4087</t>
         </is>
       </c>
       <c r="F106" s="2">
@@ -3576,7 +3576,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Financial Aid Counselor</t>
+          <t>Part-time Faculty Pool - Commercial Motor Vehicle (CMV) Driver Training Instructor</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4634</t>
+          <t>https://jobs.sheridan.edu/postings/4487</t>
         </is>
       </c>
       <c r="F108" s="2">
@@ -3606,7 +3606,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Education Instructor</t>
+          <t>Financial Aid Counselor</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4089</t>
+          <t>https://jobs.sheridan.edu/postings/4634</t>
         </is>
       </c>
       <c r="F109" s="2">
@@ -3636,7 +3636,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>(Student Position) Dental Hygiene Program Assistant</t>
+          <t>Part-time Faculty Pool - Education Instructor</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4497</t>
+          <t>https://jobs.sheridan.edu/postings/4089</t>
         </is>
       </c>
       <c r="F110" s="2">
@@ -3696,7 +3696,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>(Student Position) Campus Life &amp; Housing Office Assistant</t>
+          <t>(Student Position) Dental Hygiene Program Assistant</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4643</t>
+          <t>https://jobs.sheridan.edu/postings/4497</t>
         </is>
       </c>
       <c r="F112" s="2">
@@ -3726,7 +3726,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Life Science (Biology or A&amp;P) Instructor</t>
+          <t>(Student Position) Campus Life &amp; Housing Office Assistant</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4093</t>
+          <t>https://jobs.sheridan.edu/postings/4643</t>
         </is>
       </c>
       <c r="F113" s="2">
@@ -3756,7 +3756,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>(Student Position) Information Technology (IT) Night Helpdesk</t>
+          <t>Part-time Faculty Pool - Life Science (Biology or A&amp;P) Instructor</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4502</t>
+          <t>https://jobs.sheridan.edu/postings/4093</t>
         </is>
       </c>
       <c r="F114" s="2">
@@ -3816,27 +3816,27 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Facilities Director</t>
+          <t>(Student Position) Information Technology (IT) Night Helpdesk</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Northwest College Campus</t>
+          <t>Sheridan College Campus</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Northwest College</t>
+          <t>Sheridan College</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://northwestcollege.simplehire.com/postings/2640</t>
+          <t>https://jobs.sheridan.edu/postings/4502</t>
         </is>
       </c>
       <c r="F116" s="2">
@@ -3846,7 +3846,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Adjunct - Instructor of CAD</t>
+          <t>Facilities Director</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://northwestcollege.simplehire.com/postings/2671</t>
+          <t>https://northwestcollege.simplehire.com/postings/2640</t>
         </is>
       </c>
       <c r="F117" s="2">
@@ -3876,7 +3876,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Computing Services Analyst</t>
+          <t>Adjunct - Instructor of CAD</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://northwestcollege.simplehire.com/postings/2686</t>
+          <t>https://northwestcollege.simplehire.com/postings/2671</t>
         </is>
       </c>
       <c r="F118" s="2">
@@ -3906,7 +3906,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Counselor – Student Success Program Coordinator</t>
+          <t>Computing Services Analyst</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://northwestcollege.simplehire.com/postings/2693</t>
+          <t>https://northwestcollege.simplehire.com/postings/2686</t>
         </is>
       </c>
       <c r="F119" s="2">
@@ -3936,7 +3936,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Financial Aid Specialist</t>
+          <t>Counselor – Student Success Program Coordinator</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://northwestcollege.simplehire.com/postings/2670</t>
+          <t>https://northwestcollege.simplehire.com/postings/2693</t>
         </is>
       </c>
       <c r="F120" s="2">
@@ -3966,7 +3966,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Interim Educational Support Coordinator - Equine Program</t>
+          <t>Financial Aid Specialist</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://northwestcollege.simplehire.com/postings/2683</t>
+          <t>https://northwestcollege.simplehire.com/postings/2670</t>
         </is>
       </c>
       <c r="F121" s="2">
@@ -3996,7 +3996,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FIxed Term Instructor of Equine Studies</t>
+          <t>Interim Educational Support Coordinator - Equine Program</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://northwestcollege.simplehire.com/postings/2691</t>
+          <t>https://northwestcollege.simplehire.com/postings/2683</t>
         </is>
       </c>
       <c r="F122" s="2">
@@ -4026,27 +4026,27 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>FIxed Term Instructor of Equine Studies</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Northwest College Campus</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>University of Wyoming</t>
+          <t>Northwest College</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://northwestcollege.simplehire.com/postings/2691</t>
         </is>
       </c>
       <c r="F123" s="2">
@@ -4056,12 +4056,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F124" s="2">
@@ -4086,7 +4086,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F125" s="2">
@@ -4116,7 +4116,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F126" s="2">
@@ -4146,7 +4146,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F127" s="2">
@@ -4176,7 +4176,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F128" s="2">
@@ -4206,7 +4206,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F129" s="2">
@@ -4236,7 +4236,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F130" s="2">
@@ -4266,7 +4266,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F131" s="2">
@@ -4296,7 +4296,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F132" s="2">
@@ -4326,7 +4326,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F133" s="2">
@@ -4356,7 +4356,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F134" s="2">
@@ -4386,7 +4386,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F135" s="2">
@@ -4416,7 +4416,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F136" s="2">
@@ -4446,7 +4446,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F137" s="2">
@@ -4476,7 +4476,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F138" s="2">
@@ -4506,7 +4506,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F139" s="2">
@@ -4536,7 +4536,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F140" s="2">
@@ -4566,7 +4566,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F141" s="2">
@@ -4596,7 +4596,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F142" s="2">
@@ -4626,7 +4626,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F143" s="2">
@@ -4656,7 +4656,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F144" s="2">
@@ -4686,7 +4686,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F145" s="2">
@@ -4716,7 +4716,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F146" s="2">
@@ -4746,7 +4746,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Archives Aide Expeditor</t>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
         </is>
       </c>
       <c r="F147" s="2">
@@ -4776,17 +4776,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>Hourly Pooled - Archives Aide Expeditor</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Laramie, WY, United States</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
         </is>
       </c>
       <c r="F148" s="2">
@@ -4806,12 +4806,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F149" s="2">
@@ -4836,7 +4836,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F150" s="2">
@@ -4866,7 +4866,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F151" s="2">
@@ -4896,7 +4896,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F152" s="2">
@@ -4926,7 +4926,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F153" s="2">
@@ -4956,7 +4956,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F154" s="2">
@@ -4986,7 +4986,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F155" s="2">
@@ -5016,7 +5016,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F156" s="2">
@@ -5046,7 +5046,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F157" s="2">
@@ -5076,7 +5076,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F158" s="2">
@@ -5106,7 +5106,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F159" s="2">
@@ -5136,7 +5136,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F160" s="2">
@@ -5166,7 +5166,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F161" s="2">
@@ -5196,7 +5196,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F162" s="2">
@@ -5226,7 +5226,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F163" s="2">
@@ -5256,7 +5256,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F164" s="2">
@@ -5286,7 +5286,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F165" s="2">
@@ -5316,7 +5316,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F166" s="2">
@@ -5346,7 +5346,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F167" s="2">
@@ -5376,7 +5376,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F168" s="2">
@@ -5406,7 +5406,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F169" s="2">
@@ -5436,7 +5436,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F170" s="2">
@@ -5466,7 +5466,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F171" s="2">
@@ -5496,7 +5496,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Archives Aide Expeditor</t>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
         </is>
       </c>
       <c r="F172" s="2">
@@ -5526,17 +5526,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>Hourly Pooled - Archives Aide Expeditor</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Laramie, WY, United States</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
         </is>
       </c>
       <c r="F173" s="2">
@@ -5556,12 +5556,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F174" s="2">
@@ -5586,7 +5586,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F175" s="2">
@@ -5616,7 +5616,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F176" s="2">
@@ -5646,7 +5646,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F177" s="2">
@@ -5676,7 +5676,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F178" s="2">
@@ -5706,7 +5706,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F179" s="2">
@@ -5736,7 +5736,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F180" s="2">
@@ -5766,7 +5766,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F181" s="2">
@@ -5796,7 +5796,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F182" s="2">
@@ -5826,7 +5826,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F183" s="2">
@@ -5856,7 +5856,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F184" s="2">
@@ -5886,7 +5886,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F185" s="2">
@@ -5916,7 +5916,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F186" s="2">
@@ -5946,7 +5946,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F187" s="2">
@@ -5976,7 +5976,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F188" s="2">
@@ -6006,7 +6006,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F189" s="2">
@@ -6036,7 +6036,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F190" s="2">
@@ -6066,7 +6066,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F191" s="2">
@@ -6096,7 +6096,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F192" s="2">
@@ -6126,7 +6126,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F193" s="2">
@@ -6156,7 +6156,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F194" s="2">
@@ -6186,7 +6186,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F195" s="2">
@@ -6216,7 +6216,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F196" s="2">
@@ -6246,7 +6246,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Archives Aide Expeditor</t>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
         </is>
       </c>
       <c r="F197" s="2">
@@ -6276,17 +6276,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>Hourly Pooled - Archives Aide Expeditor</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Laramie, WY, United States</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
         </is>
       </c>
       <c r="F198" s="2">
@@ -6306,12 +6306,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F199" s="2">
@@ -6336,7 +6336,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F200" s="2">
@@ -6366,7 +6366,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F201" s="2">
@@ -6396,7 +6396,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F202" s="2">
@@ -6426,7 +6426,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F203" s="2">
@@ -6456,7 +6456,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F204" s="2">
@@ -6486,7 +6486,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F205" s="2">
@@ -6516,7 +6516,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F206" s="2">
@@ -6546,7 +6546,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F207" s="2">
@@ -6576,7 +6576,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F208" s="2">
@@ -6606,7 +6606,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F209" s="2">
@@ -6636,7 +6636,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F210" s="2">
@@ -6666,7 +6666,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F211" s="2">
@@ -6696,7 +6696,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F212" s="2">
@@ -6726,7 +6726,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F213" s="2">
@@ -6756,7 +6756,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F214" s="2">
@@ -6786,7 +6786,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F215" s="2">
@@ -6816,7 +6816,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F216" s="2">
@@ -6846,7 +6846,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F217" s="2">
@@ -6876,7 +6876,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F218" s="2">
@@ -6906,7 +6906,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F219" s="2">
@@ -6936,7 +6936,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F220" s="2">
@@ -6966,7 +6966,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F221" s="2">
@@ -6996,7 +6996,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Archives Aide Expeditor</t>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
         </is>
       </c>
       <c r="F222" s="2">
@@ -7026,17 +7026,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>Hourly Pooled - Archives Aide Expeditor</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Laramie, WY, United States</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
         </is>
       </c>
       <c r="F223" s="2">
@@ -7056,12 +7056,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F224" s="2">
@@ -7086,7 +7086,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F225" s="2">
@@ -7116,7 +7116,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F226" s="2">
@@ -7146,7 +7146,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F227" s="2">
@@ -7176,7 +7176,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F228" s="2">
@@ -7206,7 +7206,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F229" s="2">
@@ -7236,7 +7236,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F230" s="2">
@@ -7266,7 +7266,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F231" s="2">
@@ -7296,7 +7296,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F232" s="2">
@@ -7326,7 +7326,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F233" s="2">
@@ -7356,7 +7356,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F234" s="2">
@@ -7386,7 +7386,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F235" s="2">
@@ -7416,7 +7416,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F236" s="2">
@@ -7446,7 +7446,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F237" s="2">
@@ -7476,7 +7476,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F238" s="2">
@@ -7506,7 +7506,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F239" s="2">
@@ -7536,7 +7536,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F240" s="2">
@@ -7566,7 +7566,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F241" s="2">
@@ -7596,7 +7596,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F242" s="2">
@@ -7626,7 +7626,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F243" s="2">
@@ -7656,7 +7656,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F244" s="2">
@@ -7686,7 +7686,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F245" s="2">
@@ -7716,7 +7716,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F246" s="2">
@@ -7746,7 +7746,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Archives Aide Expeditor</t>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
         </is>
       </c>
       <c r="F247" s="2">
@@ -7776,17 +7776,17 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>Hourly Pooled - Archives Aide Expeditor</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Laramie, WY, United States</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
         </is>
       </c>
       <c r="F248" s="2">
@@ -7806,12 +7806,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F249" s="2">
@@ -7836,7 +7836,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F250" s="2">
@@ -7866,7 +7866,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F251" s="2">
@@ -7896,7 +7896,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F252" s="2">
@@ -7926,7 +7926,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F253" s="2">
@@ -7956,7 +7956,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F254" s="2">
@@ -7986,7 +7986,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F255" s="2">
@@ -8016,7 +8016,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F256" s="2">
@@ -8046,7 +8046,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F257" s="2">
@@ -8076,7 +8076,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F258" s="2">
@@ -8106,7 +8106,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F259" s="2">
@@ -8136,7 +8136,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F260" s="2">
@@ -8166,7 +8166,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F261" s="2">
@@ -8196,7 +8196,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F262" s="2">
@@ -8226,7 +8226,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F263" s="2">
@@ -8256,7 +8256,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F264" s="2">
@@ -8286,7 +8286,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F265" s="2">
@@ -8316,7 +8316,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F266" s="2">
@@ -8346,7 +8346,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F267" s="2">
@@ -8376,7 +8376,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -8386,7 +8386,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F268" s="2">
@@ -8406,7 +8406,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F269" s="2">
@@ -8436,7 +8436,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F270" s="2">
@@ -8466,7 +8466,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F271" s="2">
@@ -8496,7 +8496,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Archives Aide Expeditor</t>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
         </is>
       </c>
       <c r="F272" s="2">
@@ -8526,17 +8526,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>Hourly Pooled - Archives Aide Expeditor</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Laramie, WY, United States</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
         </is>
       </c>
       <c r="F273" s="2">
@@ -8556,12 +8556,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F274" s="2">
@@ -8586,7 +8586,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F275" s="2">
@@ -8616,7 +8616,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F276" s="2">
@@ -8646,7 +8646,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F277" s="2">
@@ -8676,7 +8676,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F278" s="2">
@@ -8706,7 +8706,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F279" s="2">
@@ -8736,7 +8736,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F280" s="2">
@@ -8766,7 +8766,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F281" s="2">
@@ -8796,7 +8796,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F282" s="2">
@@ -8826,7 +8826,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F283" s="2">
@@ -8856,7 +8856,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F284" s="2">
@@ -8886,7 +8886,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F285" s="2">
@@ -8916,7 +8916,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F286" s="2">
@@ -8946,7 +8946,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F287" s="2">
@@ -8976,7 +8976,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F288" s="2">
@@ -9006,7 +9006,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F289" s="2">
@@ -9036,7 +9036,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F290" s="2">
@@ -9066,7 +9066,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F291" s="2">
@@ -9096,7 +9096,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F292" s="2">
@@ -9126,7 +9126,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F293" s="2">
@@ -9156,7 +9156,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F294" s="2">
@@ -9186,7 +9186,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F295" s="2">
@@ -9216,7 +9216,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F296" s="2">
@@ -9246,7 +9246,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Archives Aide Expeditor</t>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
         </is>
       </c>
       <c r="F297" s="2">
@@ -9276,17 +9276,17 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>Hourly Pooled - Archives Aide Expeditor</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Laramie, WY, United States</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
         </is>
       </c>
       <c r="F298" s="2">
@@ -9306,12 +9306,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F299" s="2">
@@ -9336,7 +9336,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F300" s="2">
@@ -9366,7 +9366,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F301" s="2">
@@ -9396,7 +9396,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F302" s="2">
@@ -9426,7 +9426,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F303" s="2">
@@ -9456,7 +9456,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F304" s="2">
@@ -9486,7 +9486,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F305" s="2">
@@ -9516,7 +9516,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F306" s="2">
@@ -9546,7 +9546,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F307" s="2">
@@ -9576,7 +9576,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F308" s="2">
@@ -9606,7 +9606,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -9626,7 +9626,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F309" s="2">
@@ -9636,7 +9636,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F310" s="2">
@@ -9666,7 +9666,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F311" s="2">
@@ -9696,7 +9696,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F312" s="2">
@@ -9726,7 +9726,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F313" s="2">
@@ -9756,7 +9756,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -9776,7 +9776,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F314" s="2">
@@ -9786,7 +9786,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F315" s="2">
@@ -9816,7 +9816,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F316" s="2">
@@ -9846,7 +9846,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F317" s="2">
@@ -9876,7 +9876,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F318" s="2">
@@ -9906,7 +9906,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F319" s="2">
@@ -9936,7 +9936,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F320" s="2">
@@ -9966,7 +9966,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F321" s="2">
@@ -9996,7 +9996,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Archives Aide Expeditor</t>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
         </is>
       </c>
       <c r="F322" s="2">
@@ -10026,17 +10026,17 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>Hourly Pooled - Archives Aide Expeditor</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Laramie, WY, United States</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
         </is>
       </c>
       <c r="F323" s="2">
@@ -10056,12 +10056,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F324" s="2">
@@ -10086,7 +10086,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F325" s="2">
@@ -10116,7 +10116,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F326" s="2">
@@ -10146,7 +10146,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F327" s="2">
@@ -10176,7 +10176,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F328" s="2">
@@ -10206,7 +10206,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F329" s="2">
@@ -10236,7 +10236,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F330" s="2">
@@ -10266,7 +10266,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F331" s="2">
@@ -10296,7 +10296,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F332" s="2">
@@ -10326,7 +10326,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -10346,7 +10346,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F333" s="2">
@@ -10356,7 +10356,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F334" s="2">
@@ -10386,7 +10386,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F335" s="2">
@@ -10416,7 +10416,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F336" s="2">
@@ -10446,7 +10446,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F337" s="2">
@@ -10476,7 +10476,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F338" s="2">
@@ -10506,7 +10506,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F339" s="2">
@@ -10536,7 +10536,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F340" s="2">
@@ -10566,7 +10566,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F341" s="2">
@@ -10596,7 +10596,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F342" s="2">
@@ -10626,7 +10626,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -10646,7 +10646,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F343" s="2">
@@ -10656,7 +10656,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F344" s="2">
@@ -10686,7 +10686,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F345" s="2">
@@ -10716,7 +10716,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F346" s="2">
@@ -10746,30 +10746,60 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Laramie, WY, United States</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>University of Wyoming</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+        </is>
+      </c>
+      <c r="F347" s="2">
+        <v>46237</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
           <t>Hourly Pooled - Archives Aide Expeditor</t>
         </is>
       </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Laramie, WY, United States</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E347" t="inlineStr">
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>University of Wyoming</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
         <is>
           <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
         </is>
       </c>
-      <c r="F347" s="2">
+      <c r="F348" s="2">
         <v>46237</v>
       </c>
     </row>

--- a/Wy_Ed_Jobs/hedata.xlsx
+++ b/Wy_Ed_Jobs/hedata.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F348"/>
+  <dimension ref="A1:F349"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
@@ -756,27 +756,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Adjunct</t>
+          <t>Grounds Technician III</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Riverton</t>
+          <t>Casper, WY</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Posted more than 30 days ago</t>
+          <t>Posted 2 weeks ago</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Central Wyoming College</t>
+          <t>Casper College</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.schooljobs.com/careers/cwc/jobs/4125290/adjunct</t>
+          <t>https://www.schooljobs.com/careers/caspercollege/jobs/5414593/grounds-technician-iii</t>
         </is>
       </c>
       <c r="F14" s="2">
@@ -786,12 +786,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Adjunct- General for Jackson</t>
+          <t>Adjunct</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jackson</t>
+          <t>Riverton</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.schooljobs.com/careers/cwc/jobs/4503058/adjunct-general-for-jackson</t>
+          <t>https://www.schooljobs.com/careers/cwc/jobs/4125290/adjunct</t>
         </is>
       </c>
       <c r="F15" s="2">
@@ -816,12 +816,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bus Driver</t>
+          <t>Adjunct- General for Jackson</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Riverton</t>
+          <t>Jackson</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.schooljobs.com/careers/cwc/jobs/5282562/bus-driver</t>
+          <t>https://www.schooljobs.com/careers/cwc/jobs/4503058/adjunct-general-for-jackson</t>
         </is>
       </c>
       <c r="F16" s="2">
@@ -846,7 +846,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cosmetology Instructor</t>
+          <t>Bus Driver</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.schooljobs.com/careers/cwc/jobs/5326093/cosmetology-instructor</t>
+          <t>https://www.schooljobs.com/careers/cwc/jobs/5282562/bus-driver</t>
         </is>
       </c>
       <c r="F17" s="2">
@@ -876,12 +876,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Director of Development- Jackson Campus</t>
+          <t>Cosmetology Instructor</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jackson</t>
+          <t>Riverton</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.schooljobs.com/careers/cwc/jobs/5367035/director-of-development-jackson-campus</t>
+          <t>https://www.schooljobs.com/careers/cwc/jobs/5326093/cosmetology-instructor</t>
         </is>
       </c>
       <c r="F18" s="2">
@@ -906,12 +906,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Executive Director of Institutional Effectiveness &amp; Research</t>
+          <t>Director of Development- Jackson Campus</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Riverton</t>
+          <t>Jackson</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.schooljobs.com/careers/cwc/jobs/5340918/executive-director-of-institutional-effectiveness-research</t>
+          <t>https://www.schooljobs.com/careers/cwc/jobs/5367035/director-of-development-jackson-campus</t>
         </is>
       </c>
       <c r="F19" s="2">
@@ -936,7 +936,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Food Service Assistant- Line Server</t>
+          <t>Executive Director of Institutional Effectiveness &amp; Research</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Posted 1 week ago</t>
+          <t>Posted more than 30 days ago</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.schooljobs.com/careers/cwc/jobs/5421529/food-service-assistant-line-server</t>
+          <t>https://www.schooljobs.com/careers/cwc/jobs/5340918/executive-director-of-institutional-effectiveness-research</t>
         </is>
       </c>
       <c r="F20" s="2">
@@ -966,7 +966,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jackson Campus Operations Manager</t>
+          <t>Food Service Assistant- Line Server</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Posted 5 days ago</t>
+          <t>Posted 1 week ago</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://www.schooljobs.com/careers/cwc/jobs/5429594/jackson-campus-operations-manager</t>
+          <t>https://www.schooljobs.com/careers/cwc/jobs/5421529/food-service-assistant-line-server</t>
         </is>
       </c>
       <c r="F21" s="2">
@@ -996,7 +996,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Livestock Technician</t>
+          <t>Jackson Campus Operations Manager</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://www.schooljobs.com/careers/cwc/jobs/5429336/livestock-technician</t>
+          <t>https://www.schooljobs.com/careers/cwc/jobs/5429594/jackson-campus-operations-manager</t>
         </is>
       </c>
       <c r="F22" s="2">
@@ -1026,7 +1026,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nursing Instructor</t>
+          <t>Livestock Technician</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Posted more than 30 days ago</t>
+          <t>Posted 5 days ago</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.schooljobs.com/careers/cwc/jobs/5283374/nursing-instructor</t>
+          <t>https://www.schooljobs.com/careers/cwc/jobs/5429336/livestock-technician</t>
         </is>
       </c>
       <c r="F23" s="2">
@@ -1056,27 +1056,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Math Instructor</t>
+          <t>Nursing Instructor</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Eastern Wyoming Campus</t>
+          <t>Riverton</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>Posted more than 30 days ago</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Eastern Wyoming Community College</t>
+          <t>Central Wyoming College</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://ewc.peopleadmin.com/postings/1915</t>
+          <t>https://www.schooljobs.com/careers/cwc/jobs/5283374/nursing-instructor</t>
         </is>
       </c>
       <c r="F24" s="2">
@@ -1086,7 +1086,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Adjunct Business Instructor</t>
+          <t>Math Instructor</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://ewc.peopleadmin.com/postings/1936</t>
+          <t>https://ewc.peopleadmin.com/postings/1915</t>
         </is>
       </c>
       <c r="F25" s="2">
@@ -1116,7 +1116,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Adjunct Health Sciences Instructor</t>
+          <t>Adjunct Business Instructor</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://ewc.peopleadmin.com/postings/1951</t>
+          <t>https://ewc.peopleadmin.com/postings/1936</t>
         </is>
       </c>
       <c r="F26" s="2">
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Adjunct Math &amp; Science Instructor</t>
+          <t>Adjunct Health Sciences Instructor</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://ewc.peopleadmin.com/postings/1955</t>
+          <t>https://ewc.peopleadmin.com/postings/1951</t>
         </is>
       </c>
       <c r="F27" s="2">
@@ -1176,7 +1176,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Adjunct Veterinary Technology Instructor</t>
+          <t>Adjunct Math &amp; Science Instructor</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://ewc.peopleadmin.com/postings/1958</t>
+          <t>https://ewc.peopleadmin.com/postings/1955</t>
         </is>
       </c>
       <c r="F28" s="2">
@@ -1206,7 +1206,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Registrar</t>
+          <t>Adjunct Veterinary Technology Instructor</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://ewc.peopleadmin.com/postings/1964</t>
+          <t>https://ewc.peopleadmin.com/postings/1958</t>
         </is>
       </c>
       <c r="F29" s="2">
@@ -1236,7 +1236,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Custodian (Full-Time)</t>
+          <t>Registrar</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://ewc.peopleadmin.com/postings/1971</t>
+          <t>https://ewc.peopleadmin.com/postings/1964</t>
         </is>
       </c>
       <c r="F30" s="2">
@@ -1266,7 +1266,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Nursing Instructor-Torrington</t>
+          <t>Custodian (Full-Time)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://ewc.peopleadmin.com/postings/1923</t>
+          <t>https://ewc.peopleadmin.com/postings/1971</t>
         </is>
       </c>
       <c r="F31" s="2">
@@ -1296,7 +1296,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Adjunct Arts, Humantities, Social &amp; Behavioral Sciences Instructor</t>
+          <t>Nursing Instructor-Torrington</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://ewc.peopleadmin.com/postings/1950</t>
+          <t>https://ewc.peopleadmin.com/postings/1923</t>
         </is>
       </c>
       <c r="F32" s="2">
@@ -1326,7 +1326,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Adjunct Agriculture  Instructor</t>
+          <t>Adjunct Arts, Humantities, Social &amp; Behavioral Sciences Instructor</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://ewc.peopleadmin.com/postings/1952</t>
+          <t>https://ewc.peopleadmin.com/postings/1950</t>
         </is>
       </c>
       <c r="F33" s="2">
@@ -1356,7 +1356,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Adjunct College Instructor</t>
+          <t>Adjunct Agriculture  Instructor</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://ewc.peopleadmin.com/postings/1956</t>
+          <t>https://ewc.peopleadmin.com/postings/1952</t>
         </is>
       </c>
       <c r="F34" s="2">
@@ -1386,7 +1386,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Chief Financial Officer (CFO) and Associate Vice President (AVP)</t>
+          <t>Adjunct College Instructor</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://ewc.peopleadmin.com/postings/1962</t>
+          <t>https://ewc.peopleadmin.com/postings/1956</t>
         </is>
       </c>
       <c r="F35" s="2">
@@ -1416,7 +1416,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Adjunct Physics Instructor</t>
+          <t>Chief Financial Officer (CFO) and Associate Vice President (AVP)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://ewc.peopleadmin.com/postings/1966</t>
+          <t>https://ewc.peopleadmin.com/postings/1962</t>
         </is>
       </c>
       <c r="F36" s="2">
@@ -1446,27 +1446,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Accounting Adjunct Instructor</t>
+          <t>Adjunct Physics Instructor</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Gillette College Main Building</t>
+          <t>Eastern Wyoming Campus</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Posted more than 30 days ago</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Gillette College</t>
+          <t>Eastern Wyoming Community College</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://www.schooljobs.com/careers/gillettecollege/jobs/5314765/accounting-adjunct-instructor</t>
+          <t>https://ewc.peopleadmin.com/postings/1966</t>
         </is>
       </c>
       <c r="F37" s="2">
@@ -1476,7 +1476,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Adjunct Nursing Instructor</t>
+          <t>Accounting Adjunct Instructor</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://www.schooljobs.com/careers/gillettecollege/jobs/5314726/adjunct-nursing-instructor</t>
+          <t>https://www.schooljobs.com/careers/gillettecollege/jobs/5314765/accounting-adjunct-instructor</t>
         </is>
       </c>
       <c r="F38" s="2">
@@ -1506,17 +1506,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Area 59 STEM and Makerspace Instructor</t>
+          <t>Adjunct Nursing Instructor</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gillette College Technical Education Center</t>
+          <t>Gillette College Main Building</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Posted 5 days ago</t>
+          <t>Posted more than 30 days ago</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://www.schooljobs.com/careers/gillettecollege/jobs/5429236/area-59-stem-and-makerspace-instructor</t>
+          <t>https://www.schooljobs.com/careers/gillettecollege/jobs/5314726/adjunct-nursing-instructor</t>
         </is>
       </c>
       <c r="F39" s="2">
@@ -1536,17 +1536,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Art History Adjunct Instructor</t>
+          <t>Area 59 STEM and Makerspace Instructor</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Gillette College Main Building</t>
+          <t>Gillette College Technical Education Center</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Posted more than 30 days ago</t>
+          <t>Posted 5 days ago</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://www.schooljobs.com/careers/gillettecollege/jobs/5314760/art-history-adjunct-instructor</t>
+          <t>https://www.schooljobs.com/careers/gillettecollege/jobs/5429236/area-59-stem-and-makerspace-instructor</t>
         </is>
       </c>
       <c r="F40" s="2">
@@ -1566,7 +1566,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Coordinator of Residence Life &amp; Housing</t>
+          <t>Art History Adjunct Instructor</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://www.schooljobs.com/careers/gillettecollege/jobs/5396856/coordinator-of-residence-life-housing</t>
+          <t>https://www.schooljobs.com/careers/gillettecollege/jobs/5314760/art-history-adjunct-instructor</t>
         </is>
       </c>
       <c r="F41" s="2">
@@ -1596,7 +1596,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Criminal Justice Forensic Psych Adjunct Instructor</t>
+          <t>Coordinator of Residence Life &amp; Housing</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://www.schooljobs.com/careers/gillettecollege/jobs/5314753/criminal-justice-forensic-psych-adjunct-instructor</t>
+          <t>https://www.schooljobs.com/careers/gillettecollege/jobs/5396856/coordinator-of-residence-life-housing</t>
         </is>
       </c>
       <c r="F42" s="2">
@@ -1626,7 +1626,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Director of Residence Life and Housing</t>
+          <t>Criminal Justice Forensic Psych Adjunct Instructor</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://www.schooljobs.com/careers/gillettecollege/jobs/5380917/director-of-residence-life-and-housing</t>
+          <t>https://www.schooljobs.com/careers/gillettecollege/jobs/5314753/criminal-justice-forensic-psych-adjunct-instructor</t>
         </is>
       </c>
       <c r="F43" s="2">
@@ -1656,12 +1656,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Enterprise System Administrator - Azure</t>
+          <t>Director of Residence Life and Housing</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gillette College Technical Education Center</t>
+          <t>Gillette College Main Building</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://www.schooljobs.com/careers/gillettecollege/jobs/5314772/enterprise-system-administrator-azure</t>
+          <t>https://www.schooljobs.com/careers/gillettecollege/jobs/5380917/director-of-residence-life-and-housing</t>
         </is>
       </c>
       <c r="F44" s="2">
@@ -1686,12 +1686,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Laboratory Assistant</t>
+          <t>Enterprise System Administrator - Azure</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Gillette College Main Building</t>
+          <t>Gillette College Technical Education Center</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://www.schooljobs.com/careers/gillettecollege/jobs/5396875/laboratory-assistant</t>
+          <t>https://www.schooljobs.com/careers/gillettecollege/jobs/5314772/enterprise-system-administrator-azure</t>
         </is>
       </c>
       <c r="F45" s="2">
@@ -1716,7 +1716,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Library Aide</t>
+          <t>Laboratory Assistant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://www.schooljobs.com/careers/gillettecollege/jobs/5354460/library-aide</t>
+          <t>https://www.schooljobs.com/careers/gillettecollege/jobs/5396875/laboratory-assistant</t>
         </is>
       </c>
       <c r="F46" s="2">
@@ -1746,27 +1746,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Spanish Instructor</t>
+          <t>Library Aide</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sheridan College Campus</t>
+          <t>Gillette College Main Building</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>Posted more than 30 days ago</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sheridan College</t>
+          <t>Gillette College</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4095</t>
+          <t>https://www.schooljobs.com/careers/gillettecollege/jobs/5354460/library-aide</t>
         </is>
       </c>
       <c r="F47" s="2">
@@ -1806,7 +1806,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Advanced Manufacturing Instructor</t>
+          <t>Part-time Faculty Pool - Spanish Instructor</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3939</t>
+          <t>https://jobs.sheridan.edu/postings/4095</t>
         </is>
       </c>
       <c r="F49" s="2">
@@ -1866,7 +1866,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Composites Manufacturing</t>
+          <t>Part-time Faculty Pool - Advanced Manufacturing Instructor</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4097</t>
+          <t>https://jobs.sheridan.edu/postings/3939</t>
         </is>
       </c>
       <c r="F51" s="2">
@@ -1926,7 +1926,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Part-time Academic Support Services Pool- Academic Support Tutor</t>
+          <t>Part-time Faculty Pool - Composites Manufacturing</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3968</t>
+          <t>https://jobs.sheridan.edu/postings/4097</t>
         </is>
       </c>
       <c r="F53" s="2">
@@ -1986,7 +1986,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Construction Instructor</t>
+          <t>Part-time Academic Support Services Pool- Academic Support Tutor</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4099</t>
+          <t>https://jobs.sheridan.edu/postings/3968</t>
         </is>
       </c>
       <c r="F55" s="2">
@@ -2076,7 +2076,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>(Student Position) Writing Center Peer Consultant</t>
+          <t>Part-time Faculty Pool - Construction Instructor</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4521</t>
+          <t>https://jobs.sheridan.edu/postings/4099</t>
         </is>
       </c>
       <c r="F58" s="2">
@@ -2136,7 +2136,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Music Instructor</t>
+          <t>(Student Position) Writing Center Peer Consultant</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4102</t>
+          <t>https://jobs.sheridan.edu/postings/4521</t>
         </is>
       </c>
       <c r="F60" s="2">
@@ -2226,7 +2226,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>(Student Position )Library Helpdesk</t>
+          <t>Part-time Faculty Pool - Music Instructor</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4525</t>
+          <t>https://jobs.sheridan.edu/postings/4102</t>
         </is>
       </c>
       <c r="F63" s="2">
@@ -2286,7 +2286,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>(Student Position) Youth Soccer Referee - YMCA</t>
+          <t>(Student Position )Library Helpdesk</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4681</t>
+          <t>https://jobs.sheridan.edu/postings/4525</t>
         </is>
       </c>
       <c r="F65" s="2">
@@ -2316,7 +2316,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Electrical Apprenticeship Instructor</t>
+          <t>Part-time Faculty Pool - Astronomy Instructor</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2022-08-03</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4197</t>
+          <t>https://jobs.sheridan.edu/postings/3311</t>
         </is>
       </c>
       <c r="F66" s="2">
@@ -2346,7 +2346,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Astronomy Instructor</t>
+          <t>(Student Position) Youth Soccer Referee - YMCA</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2022-08-03</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3311</t>
+          <t>https://jobs.sheridan.edu/postings/4681</t>
         </is>
       </c>
       <c r="F67" s="2">
@@ -2376,7 +2376,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Residential Life Coordinator</t>
+          <t>Part-time Faculty Pool - Electrical Apprenticeship Instructor</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4568</t>
+          <t>https://jobs.sheridan.edu/postings/4197</t>
         </is>
       </c>
       <c r="F68" s="2">
@@ -2436,7 +2436,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Machine Tool Instructor</t>
+          <t>Residential Life Coordinator</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4471</t>
+          <t>https://jobs.sheridan.edu/postings/4568</t>
         </is>
       </c>
       <c r="F70" s="2">
@@ -2466,7 +2466,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Culinary Instructor</t>
+          <t>Part-time Faculty Pool - Machine Tool Instructor</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3690</t>
+          <t>https://jobs.sheridan.edu/postings/4471</t>
         </is>
       </c>
       <c r="F71" s="2">
@@ -2496,7 +2496,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Enrollment Counselor</t>
+          <t>Part-time Faculty Pool - Culinary Instructor</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4633</t>
+          <t>https://jobs.sheridan.edu/postings/3690</t>
         </is>
       </c>
       <c r="F72" s="2">
@@ -2556,7 +2556,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Adobe Creative Cloud Instructor</t>
+          <t>Enrollment Counselor</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3759</t>
+          <t>https://jobs.sheridan.edu/postings/4633</t>
         </is>
       </c>
       <c r="F74" s="2">
@@ -2616,7 +2616,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>(Student Position) TRCC Information Desk Attendant</t>
+          <t>Part-time Faculty Pool - Adobe Creative Cloud Instructor</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4641</t>
+          <t>https://jobs.sheridan.edu/postings/3759</t>
         </is>
       </c>
       <c r="F76" s="2">
@@ -2676,7 +2676,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Accounting Instructor</t>
+          <t>(Student Position) TRCC Information Desk Attendant</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3763</t>
+          <t>https://jobs.sheridan.edu/postings/4641</t>
         </is>
       </c>
       <c r="F78" s="2">
@@ -2736,7 +2736,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Geology Instructor</t>
+          <t>Part-time Faculty Pool - Accounting Instructor</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4094</t>
+          <t>https://jobs.sheridan.edu/postings/3763</t>
         </is>
       </c>
       <c r="F80" s="2">
@@ -2796,7 +2796,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Math Instructor</t>
+          <t>Part-time Faculty Pool - Geology Instructor</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3938</t>
+          <t>https://jobs.sheridan.edu/postings/4094</t>
         </is>
       </c>
       <c r="F82" s="2">
@@ -2856,7 +2856,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Communications Instructor</t>
+          <t>Part-time Faculty Pool - Math Instructor</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4096</t>
+          <t>https://jobs.sheridan.edu/postings/3938</t>
         </is>
       </c>
       <c r="F84" s="2">
@@ -2916,7 +2916,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - HVAC Apprenticeship Instructor</t>
+          <t>Part-time Faculty Pool - Communications Instructor</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3940</t>
+          <t>https://jobs.sheridan.edu/postings/4096</t>
         </is>
       </c>
       <c r="F86" s="2">
@@ -2976,7 +2976,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - History Instructor</t>
+          <t>Part-time Faculty Pool - HVAC Apprenticeship Instructor</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4098</t>
+          <t>https://jobs.sheridan.edu/postings/3940</t>
         </is>
       </c>
       <c r="F88" s="2">
@@ -3036,7 +3036,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>(Student Position) Financial Aid Office Assistant</t>
+          <t>Part-time Faculty Pool - History Instructor</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4519</t>
+          <t>https://jobs.sheridan.edu/postings/4098</t>
         </is>
       </c>
       <c r="F90" s="2">
@@ -3066,7 +3066,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Health and Human Performance Instructor</t>
+          <t>(Student Position) Financial Aid Office Assistant</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3983</t>
+          <t>https://jobs.sheridan.edu/postings/4519</t>
         </is>
       </c>
       <c r="F91" s="2">
@@ -3096,7 +3096,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Hospitality/Tourism</t>
+          <t>Part-time Faculty Pool - Health and Human Performance Instructor</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4101</t>
+          <t>https://jobs.sheridan.edu/postings/3983</t>
         </is>
       </c>
       <c r="F92" s="2">
@@ -3186,7 +3186,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>(Student Position) Peer Tutor</t>
+          <t>Part-time Faculty Pool - Hospitality/Tourism</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4523</t>
+          <t>https://jobs.sheridan.edu/postings/4101</t>
         </is>
       </c>
       <c r="F95" s="2">
@@ -3246,7 +3246,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Engineering Science and Engineering Tech Instructor</t>
+          <t>(Student Position) Peer Tutor</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4103</t>
+          <t>https://jobs.sheridan.edu/postings/4523</t>
         </is>
       </c>
       <c r="F97" s="2">
@@ -3336,7 +3336,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>(Student Position) Box Office Assistant</t>
+          <t>Part-time Faculty Pool - Engineering Science and Engineering Tech Instructor</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4560</t>
+          <t>https://jobs.sheridan.edu/postings/4103</t>
         </is>
       </c>
       <c r="F100" s="2">
@@ -3396,7 +3396,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Vice President of Academic Affairs</t>
+          <t>(Student Position) Box Office Assistant</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4682</t>
+          <t>https://jobs.sheridan.edu/postings/4560</t>
         </is>
       </c>
       <c r="F102" s="2">
@@ -3426,7 +3426,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Welding Instructor</t>
+          <t>Part-time Faculty Pool - Nursing Instructor</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2022-08-16</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4470</t>
+          <t>https://jobs.sheridan.edu/postings/3326</t>
         </is>
       </c>
       <c r="F103" s="2">
@@ -3456,7 +3456,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Nursing Instructor</t>
+          <t>Vice President of Academic Affairs</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2022-08-16</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3326</t>
+          <t>https://jobs.sheridan.edu/postings/4682</t>
         </is>
       </c>
       <c r="F104" s="2">
@@ -3486,7 +3486,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>(Student Position) 3D Technician</t>
+          <t>Part-time Faculty Pool - Welding Instructor</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4580</t>
+          <t>https://jobs.sheridan.edu/postings/4470</t>
         </is>
       </c>
       <c r="F105" s="2">
@@ -3546,7 +3546,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Art Instructor</t>
+          <t>(Student Position) 3D Technician</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3757</t>
+          <t>https://jobs.sheridan.edu/postings/4580</t>
         </is>
       </c>
       <c r="F107" s="2">
@@ -3606,7 +3606,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Financial Aid Counselor</t>
+          <t>Part-time Faculty Pool - Art Instructor</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4634</t>
+          <t>https://jobs.sheridan.edu/postings/3757</t>
         </is>
       </c>
       <c r="F109" s="2">
@@ -3666,7 +3666,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Business Instructor</t>
+          <t>Financial Aid Counselor</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3760</t>
+          <t>https://jobs.sheridan.edu/postings/4634</t>
         </is>
       </c>
       <c r="F111" s="2">
@@ -3726,7 +3726,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>(Student Position) Campus Life &amp; Housing Office Assistant</t>
+          <t>Part-time Faculty Pool - Business Instructor</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4643</t>
+          <t>https://jobs.sheridan.edu/postings/3760</t>
         </is>
       </c>
       <c r="F113" s="2">
@@ -3756,7 +3756,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Life Science (Biology or A&amp;P) Instructor</t>
+          <t>(Student Position) Campus Life &amp; Housing Office Assistant</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4093</t>
+          <t>https://jobs.sheridan.edu/postings/4643</t>
         </is>
       </c>
       <c r="F114" s="2">
@@ -3786,7 +3786,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Agriculture Instructor</t>
+          <t>Part-time Faculty Pool - Life Science (Biology or A&amp;P) Instructor</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3852</t>
+          <t>https://jobs.sheridan.edu/postings/4093</t>
         </is>
       </c>
       <c r="F115" s="2">
@@ -3846,27 +3846,27 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Facilities Director</t>
+          <t>Part-time Faculty Pool - Agriculture Instructor</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Northwest College Campus</t>
+          <t>Sheridan College Campus</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Northwest College</t>
+          <t>Sheridan College</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://northwestcollege.simplehire.com/postings/2640</t>
+          <t>https://jobs.sheridan.edu/postings/3852</t>
         </is>
       </c>
       <c r="F117" s="2">
@@ -3876,7 +3876,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Adjunct - Instructor of CAD</t>
+          <t>Facilities Director</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://northwestcollege.simplehire.com/postings/2671</t>
+          <t>https://northwestcollege.simplehire.com/postings/2640</t>
         </is>
       </c>
       <c r="F118" s="2">
@@ -3906,7 +3906,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Computing Services Analyst</t>
+          <t>Adjunct - Instructor of CAD</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://northwestcollege.simplehire.com/postings/2686</t>
+          <t>https://northwestcollege.simplehire.com/postings/2671</t>
         </is>
       </c>
       <c r="F119" s="2">
@@ -3936,7 +3936,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Counselor – Student Success Program Coordinator</t>
+          <t>Computing Services Analyst</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://northwestcollege.simplehire.com/postings/2693</t>
+          <t>https://northwestcollege.simplehire.com/postings/2686</t>
         </is>
       </c>
       <c r="F120" s="2">
@@ -3966,7 +3966,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Financial Aid Specialist</t>
+          <t>Counselor – Student Success Program Coordinator</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://northwestcollege.simplehire.com/postings/2670</t>
+          <t>https://northwestcollege.simplehire.com/postings/2693</t>
         </is>
       </c>
       <c r="F121" s="2">
@@ -3996,7 +3996,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Interim Educational Support Coordinator - Equine Program</t>
+          <t>Financial Aid Specialist</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://northwestcollege.simplehire.com/postings/2683</t>
+          <t>https://northwestcollege.simplehire.com/postings/2670</t>
         </is>
       </c>
       <c r="F122" s="2">
@@ -4026,7 +4026,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FIxed Term Instructor of Equine Studies</t>
+          <t>Interim Educational Support Coordinator - Equine Program</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://northwestcollege.simplehire.com/postings/2691</t>
+          <t>https://northwestcollege.simplehire.com/postings/2683</t>
         </is>
       </c>
       <c r="F123" s="2">
@@ -4056,27 +4056,27 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>FIxed Term Instructor of Equine Studies</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Northwest College Campus</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>University of Wyoming</t>
+          <t>Northwest College</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://northwestcollege.simplehire.com/postings/2691</t>
         </is>
       </c>
       <c r="F124" s="2">
@@ -4086,12 +4086,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F125" s="2">
@@ -4116,7 +4116,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F126" s="2">
@@ -4146,7 +4146,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F127" s="2">
@@ -4176,7 +4176,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F128" s="2">
@@ -4206,7 +4206,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F129" s="2">
@@ -4236,7 +4236,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F130" s="2">
@@ -4266,7 +4266,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F131" s="2">
@@ -4296,7 +4296,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F132" s="2">
@@ -4326,7 +4326,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F133" s="2">
@@ -4356,7 +4356,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F134" s="2">
@@ -4386,7 +4386,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F135" s="2">
@@ -4416,7 +4416,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F136" s="2">
@@ -4446,7 +4446,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F137" s="2">
@@ -4476,7 +4476,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F138" s="2">
@@ -4506,7 +4506,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F139" s="2">
@@ -4536,7 +4536,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F140" s="2">
@@ -4566,7 +4566,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F141" s="2">
@@ -4596,7 +4596,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F142" s="2">
@@ -4626,7 +4626,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F143" s="2">
@@ -4656,7 +4656,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F144" s="2">
@@ -4686,7 +4686,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F145" s="2">
@@ -4716,7 +4716,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F146" s="2">
@@ -4746,7 +4746,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F147" s="2">
@@ -4776,7 +4776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Archives Aide Expeditor</t>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
         </is>
       </c>
       <c r="F148" s="2">
@@ -4806,17 +4806,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>Hourly Pooled - Archives Aide Expeditor</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Laramie, WY, United States</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
         </is>
       </c>
       <c r="F149" s="2">
@@ -4836,12 +4836,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F150" s="2">
@@ -4866,7 +4866,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F151" s="2">
@@ -4896,7 +4896,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F152" s="2">
@@ -4926,7 +4926,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F153" s="2">
@@ -4956,7 +4956,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F154" s="2">
@@ -4986,7 +4986,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F155" s="2">
@@ -5016,7 +5016,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F156" s="2">
@@ -5046,7 +5046,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F157" s="2">
@@ -5076,7 +5076,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F158" s="2">
@@ -5106,7 +5106,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F159" s="2">
@@ -5136,7 +5136,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F160" s="2">
@@ -5166,7 +5166,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F161" s="2">
@@ -5196,7 +5196,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F162" s="2">
@@ -5226,7 +5226,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F163" s="2">
@@ -5256,7 +5256,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F164" s="2">
@@ -5286,7 +5286,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F165" s="2">
@@ -5316,7 +5316,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F166" s="2">
@@ -5346,7 +5346,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F167" s="2">
@@ -5376,7 +5376,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F168" s="2">
@@ -5406,7 +5406,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F169" s="2">
@@ -5436,7 +5436,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F170" s="2">
@@ -5466,7 +5466,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F171" s="2">
@@ -5496,7 +5496,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F172" s="2">
@@ -5526,7 +5526,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Archives Aide Expeditor</t>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
         </is>
       </c>
       <c r="F173" s="2">
@@ -5556,17 +5556,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>Hourly Pooled - Archives Aide Expeditor</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Laramie, WY, United States</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
         </is>
       </c>
       <c r="F174" s="2">
@@ -5586,12 +5586,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F175" s="2">
@@ -5616,7 +5616,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F176" s="2">
@@ -5646,7 +5646,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F177" s="2">
@@ -5676,7 +5676,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F178" s="2">
@@ -5706,7 +5706,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F179" s="2">
@@ -5736,7 +5736,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F180" s="2">
@@ -5766,7 +5766,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F181" s="2">
@@ -5796,7 +5796,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F182" s="2">
@@ -5826,7 +5826,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F183" s="2">
@@ -5856,7 +5856,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F184" s="2">
@@ -5886,7 +5886,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F185" s="2">
@@ -5916,7 +5916,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F186" s="2">
@@ -5946,7 +5946,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F187" s="2">
@@ -5976,7 +5976,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F188" s="2">
@@ -6006,7 +6006,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F189" s="2">
@@ -6036,7 +6036,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F190" s="2">
@@ -6066,7 +6066,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F191" s="2">
@@ -6096,7 +6096,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F192" s="2">
@@ -6126,7 +6126,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F193" s="2">
@@ -6156,7 +6156,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F194" s="2">
@@ -6186,7 +6186,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F195" s="2">
@@ -6216,7 +6216,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F196" s="2">
@@ -6246,7 +6246,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F197" s="2">
@@ -6276,7 +6276,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Archives Aide Expeditor</t>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
         </is>
       </c>
       <c r="F198" s="2">
@@ -6306,17 +6306,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>Hourly Pooled - Archives Aide Expeditor</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Laramie, WY, United States</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
         </is>
       </c>
       <c r="F199" s="2">
@@ -6336,12 +6336,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F200" s="2">
@@ -6366,7 +6366,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F201" s="2">
@@ -6396,7 +6396,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F202" s="2">
@@ -6426,7 +6426,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F203" s="2">
@@ -6456,7 +6456,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F204" s="2">
@@ -6486,7 +6486,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F205" s="2">
@@ -6516,7 +6516,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F206" s="2">
@@ -6546,7 +6546,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F207" s="2">
@@ -6576,7 +6576,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F208" s="2">
@@ -6606,7 +6606,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F209" s="2">
@@ -6636,7 +6636,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F210" s="2">
@@ -6666,7 +6666,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6676,7 +6676,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F211" s="2">
@@ -6696,7 +6696,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F212" s="2">
@@ -6726,7 +6726,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F213" s="2">
@@ -6756,7 +6756,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F214" s="2">
@@ -6786,7 +6786,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F215" s="2">
@@ -6816,7 +6816,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F216" s="2">
@@ -6846,7 +6846,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F217" s="2">
@@ -6876,7 +6876,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F218" s="2">
@@ -6906,7 +6906,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F219" s="2">
@@ -6936,7 +6936,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F220" s="2">
@@ -6966,7 +6966,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F221" s="2">
@@ -6996,7 +6996,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F222" s="2">
@@ -7026,7 +7026,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Archives Aide Expeditor</t>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
         </is>
       </c>
       <c r="F223" s="2">
@@ -7056,17 +7056,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>Hourly Pooled - Archives Aide Expeditor</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Laramie, WY, United States</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
         </is>
       </c>
       <c r="F224" s="2">
@@ -7086,12 +7086,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F225" s="2">
@@ -7116,7 +7116,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F226" s="2">
@@ -7146,7 +7146,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F227" s="2">
@@ -7176,7 +7176,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F228" s="2">
@@ -7206,7 +7206,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F229" s="2">
@@ -7236,7 +7236,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F230" s="2">
@@ -7266,7 +7266,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F231" s="2">
@@ -7296,7 +7296,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F232" s="2">
@@ -7326,7 +7326,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F233" s="2">
@@ -7356,7 +7356,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F234" s="2">
@@ -7386,7 +7386,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F235" s="2">
@@ -7416,7 +7416,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F236" s="2">
@@ -7446,7 +7446,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F237" s="2">
@@ -7476,7 +7476,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F238" s="2">
@@ -7506,7 +7506,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F239" s="2">
@@ -7536,7 +7536,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F240" s="2">
@@ -7566,7 +7566,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F241" s="2">
@@ -7596,7 +7596,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F242" s="2">
@@ -7626,7 +7626,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F243" s="2">
@@ -7656,7 +7656,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F244" s="2">
@@ -7686,7 +7686,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F245" s="2">
@@ -7716,7 +7716,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F246" s="2">
@@ -7746,7 +7746,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F247" s="2">
@@ -7776,7 +7776,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Archives Aide Expeditor</t>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
         </is>
       </c>
       <c r="F248" s="2">
@@ -7806,17 +7806,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>Hourly Pooled - Archives Aide Expeditor</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Laramie, WY, United States</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
         </is>
       </c>
       <c r="F249" s="2">
@@ -7836,12 +7836,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F250" s="2">
@@ -7866,7 +7866,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F251" s="2">
@@ -7896,7 +7896,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F252" s="2">
@@ -7926,7 +7926,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F253" s="2">
@@ -7956,7 +7956,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F254" s="2">
@@ -7986,7 +7986,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F255" s="2">
@@ -8016,7 +8016,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F256" s="2">
@@ -8046,7 +8046,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F257" s="2">
@@ -8076,7 +8076,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F258" s="2">
@@ -8106,7 +8106,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F259" s="2">
@@ -8136,7 +8136,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F260" s="2">
@@ -8166,7 +8166,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F261" s="2">
@@ -8196,7 +8196,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F262" s="2">
@@ -8226,7 +8226,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F263" s="2">
@@ -8256,7 +8256,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F264" s="2">
@@ -8286,7 +8286,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F265" s="2">
@@ -8316,7 +8316,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F266" s="2">
@@ -8346,7 +8346,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F267" s="2">
@@ -8376,7 +8376,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F268" s="2">
@@ -8406,7 +8406,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F269" s="2">
@@ -8436,7 +8436,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F270" s="2">
@@ -8466,7 +8466,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F271" s="2">
@@ -8496,7 +8496,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F272" s="2">
@@ -8526,7 +8526,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Archives Aide Expeditor</t>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
         </is>
       </c>
       <c r="F273" s="2">
@@ -8556,17 +8556,17 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>Hourly Pooled - Archives Aide Expeditor</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Laramie, WY, United States</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
         </is>
       </c>
       <c r="F274" s="2">
@@ -8586,12 +8586,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F275" s="2">
@@ -8616,7 +8616,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F276" s="2">
@@ -8646,7 +8646,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F277" s="2">
@@ -8676,7 +8676,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F278" s="2">
@@ -8706,7 +8706,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F279" s="2">
@@ -8736,7 +8736,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F280" s="2">
@@ -8766,7 +8766,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F281" s="2">
@@ -8796,7 +8796,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F282" s="2">
@@ -8826,7 +8826,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F283" s="2">
@@ -8856,7 +8856,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F284" s="2">
@@ -8886,7 +8886,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F285" s="2">
@@ -8916,7 +8916,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F286" s="2">
@@ -8946,7 +8946,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F287" s="2">
@@ -8976,7 +8976,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F288" s="2">
@@ -9006,7 +9006,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F289" s="2">
@@ -9036,7 +9036,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F290" s="2">
@@ -9066,7 +9066,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F291" s="2">
@@ -9096,7 +9096,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F292" s="2">
@@ -9126,7 +9126,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F293" s="2">
@@ -9156,7 +9156,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F294" s="2">
@@ -9186,7 +9186,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F295" s="2">
@@ -9216,7 +9216,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F296" s="2">
@@ -9246,7 +9246,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F297" s="2">
@@ -9276,7 +9276,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Archives Aide Expeditor</t>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
         </is>
       </c>
       <c r="F298" s="2">
@@ -9306,17 +9306,17 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>Hourly Pooled - Archives Aide Expeditor</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Laramie, WY, United States</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
         </is>
       </c>
       <c r="F299" s="2">
@@ -9336,12 +9336,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F300" s="2">
@@ -9366,7 +9366,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F301" s="2">
@@ -9396,7 +9396,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F302" s="2">
@@ -9426,7 +9426,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F303" s="2">
@@ -9456,7 +9456,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F304" s="2">
@@ -9486,7 +9486,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F305" s="2">
@@ -9516,7 +9516,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F306" s="2">
@@ -9546,7 +9546,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F307" s="2">
@@ -9576,7 +9576,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F308" s="2">
@@ -9606,7 +9606,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -9626,7 +9626,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F309" s="2">
@@ -9636,7 +9636,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F310" s="2">
@@ -9666,7 +9666,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -9676,7 +9676,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F311" s="2">
@@ -9696,7 +9696,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F312" s="2">
@@ -9726,7 +9726,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F313" s="2">
@@ -9756,7 +9756,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -9776,7 +9776,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F314" s="2">
@@ -9786,7 +9786,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F315" s="2">
@@ -9816,7 +9816,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F316" s="2">
@@ -9846,7 +9846,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F317" s="2">
@@ -9876,7 +9876,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F318" s="2">
@@ -9906,7 +9906,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F319" s="2">
@@ -9936,7 +9936,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F320" s="2">
@@ -9966,7 +9966,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F321" s="2">
@@ -9996,7 +9996,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F322" s="2">
@@ -10026,7 +10026,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Archives Aide Expeditor</t>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
         </is>
       </c>
       <c r="F323" s="2">
@@ -10056,17 +10056,17 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>Hourly Pooled - Archives Aide Expeditor</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Laramie, WY, United States</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
         </is>
       </c>
       <c r="F324" s="2">
@@ -10086,12 +10086,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F325" s="2">
@@ -10116,7 +10116,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F326" s="2">
@@ -10146,7 +10146,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F327" s="2">
@@ -10176,7 +10176,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F328" s="2">
@@ -10206,7 +10206,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F329" s="2">
@@ -10236,7 +10236,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F330" s="2">
@@ -10266,7 +10266,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F331" s="2">
@@ -10296,7 +10296,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F332" s="2">
@@ -10326,7 +10326,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -10346,7 +10346,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F333" s="2">
@@ -10356,7 +10356,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F334" s="2">
@@ -10386,7 +10386,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F335" s="2">
@@ -10416,7 +10416,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F336" s="2">
@@ -10446,7 +10446,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F337" s="2">
@@ -10476,7 +10476,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F338" s="2">
@@ -10506,7 +10506,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F339" s="2">
@@ -10536,7 +10536,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F340" s="2">
@@ -10566,7 +10566,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F341" s="2">
@@ -10596,7 +10596,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F342" s="2">
@@ -10626,7 +10626,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -10646,7 +10646,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F343" s="2">
@@ -10656,7 +10656,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F344" s="2">
@@ -10686,7 +10686,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F345" s="2">
@@ -10716,7 +10716,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F346" s="2">
@@ -10746,7 +10746,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F347" s="2">
@@ -10776,30 +10776,60 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Laramie, WY, United States</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>University of Wyoming</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+        </is>
+      </c>
+      <c r="F348" s="2">
+        <v>46237</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
           <t>Hourly Pooled - Archives Aide Expeditor</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Laramie, WY, United States</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E348" t="inlineStr">
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>University of Wyoming</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
         <is>
           <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
         </is>
       </c>
-      <c r="F348" s="2">
+      <c r="F349" s="2">
         <v>46237</v>
       </c>
     </row>

--- a/Wy_Ed_Jobs/hedata.xlsx
+++ b/Wy_Ed_Jobs/hedata.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F349"/>
+  <dimension ref="A1:F350"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
@@ -1776,7 +1776,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>(Student Position) Sports and Recreation Assistant</t>
+          <t>Part-time Faculty Pool - Spanish Instructor</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4647</t>
+          <t>https://jobs.sheridan.edu/postings/4095</t>
         </is>
       </c>
       <c r="F48" s="2">
@@ -1806,7 +1806,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Spanish Instructor</t>
+          <t>(Student Position) Sports and Recreation Assistant</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4095</t>
+          <t>https://jobs.sheridan.edu/postings/4647</t>
         </is>
       </c>
       <c r="F49" s="2">
@@ -1836,7 +1836,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>(Student Position) Science Lab Assistant</t>
+          <t>Part-time Faculty Pool - Advanced Manufacturing Instructor</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4511</t>
+          <t>https://jobs.sheridan.edu/postings/3939</t>
         </is>
       </c>
       <c r="F50" s="2">
@@ -1866,7 +1866,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Advanced Manufacturing Instructor</t>
+          <t>(Student Position) Science Lab Assistant</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3939</t>
+          <t>https://jobs.sheridan.edu/postings/4511</t>
         </is>
       </c>
       <c r="F51" s="2">
@@ -1896,7 +1896,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>(Student Position) Outdoor Recreation Assistant</t>
+          <t>Part-time Faculty Pool - Composites Manufacturing</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4651</t>
+          <t>https://jobs.sheridan.edu/postings/4097</t>
         </is>
       </c>
       <c r="F52" s="2">
@@ -1926,7 +1926,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Composites Manufacturing</t>
+          <t>(Student Position) Outdoor Recreation Assistant</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4097</t>
+          <t>https://jobs.sheridan.edu/postings/4651</t>
         </is>
       </c>
       <c r="F53" s="2">
@@ -2016,7 +2016,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - English Instructor</t>
+          <t>Part-time Faculty Pool - Construction Instructor</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/2725</t>
+          <t>https://jobs.sheridan.edu/postings/4099</t>
         </is>
       </c>
       <c r="F56" s="2">
@@ -2046,7 +2046,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Hospitality Faculty Coordinator</t>
+          <t>Part-time Faculty Pool - English Instructor</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4660</t>
+          <t>https://jobs.sheridan.edu/postings/2725</t>
         </is>
       </c>
       <c r="F57" s="2">
@@ -2076,7 +2076,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Construction Instructor</t>
+          <t>Hospitality Faculty Coordinator</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4099</t>
+          <t>https://jobs.sheridan.edu/postings/4660</t>
         </is>
       </c>
       <c r="F58" s="2">
@@ -2106,7 +2106,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Acting II Instructor</t>
+          <t>(Student Position) Writing Center Peer Consultant</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3985</t>
+          <t>https://jobs.sheridan.edu/postings/4521</t>
         </is>
       </c>
       <c r="F59" s="2">
@@ -2136,7 +2136,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>(Student Position) Writing Center Peer Consultant</t>
+          <t>Part-time Faculty Pool - Acting II Instructor</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4521</t>
+          <t>https://jobs.sheridan.edu/postings/3985</t>
         </is>
       </c>
       <c r="F60" s="2">
@@ -2166,7 +2166,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - History Instructor</t>
+          <t>Part-time Faculty Pool - Music Instructor</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2022-03-31</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/2981</t>
+          <t>https://jobs.sheridan.edu/postings/4102</t>
         </is>
       </c>
       <c r="F61" s="2">
@@ -2196,7 +2196,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>(Student Position) Afterschool Group Leader (K-5th Grade) - YMCA</t>
+          <t>Part-time Faculty Pool - History Instructor</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2022-03-31</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4676</t>
+          <t>https://jobs.sheridan.edu/postings/2981</t>
         </is>
       </c>
       <c r="F62" s="2">
@@ -2226,7 +2226,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Music Instructor</t>
+          <t>(Student Position) Afterschool Group Leader (K-5th Grade) - YMCA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4102</t>
+          <t>https://jobs.sheridan.edu/postings/4676</t>
         </is>
       </c>
       <c r="F63" s="2">
@@ -2256,7 +2256,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Community Interest (CI) Johnson County</t>
+          <t>(Student Position )Library Helpdesk</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4084</t>
+          <t>https://jobs.sheridan.edu/postings/4525</t>
         </is>
       </c>
       <c r="F64" s="2">
@@ -2286,7 +2286,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>(Student Position )Library Helpdesk</t>
+          <t>Part-time Faculty Pool - Community Interest (CI) Johnson County</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4525</t>
+          <t>https://jobs.sheridan.edu/postings/4084</t>
         </is>
       </c>
       <c r="F65" s="2">
@@ -2316,7 +2316,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Astronomy Instructor</t>
+          <t>(Student Position) Youth Soccer Referee - YMCA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2022-08-03</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3311</t>
+          <t>https://jobs.sheridan.edu/postings/4681</t>
         </is>
       </c>
       <c r="F66" s="2">
@@ -2346,7 +2346,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>(Student Position) Youth Soccer Referee - YMCA</t>
+          <t>Part-time Faculty Pool - Electrical Apprenticeship Instructor</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4681</t>
+          <t>https://jobs.sheridan.edu/postings/4197</t>
         </is>
       </c>
       <c r="F67" s="2">
@@ -2376,7 +2376,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Electrical Apprenticeship Instructor</t>
+          <t>Part-time Faculty Pool - Astronomy Instructor</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2022-08-03</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4197</t>
+          <t>https://jobs.sheridan.edu/postings/3311</t>
         </is>
       </c>
       <c r="F68" s="2">
@@ -2406,7 +2406,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Online Criminal Justice Instructor</t>
+          <t>Residential Life Coordinator</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4086</t>
+          <t>https://jobs.sheridan.edu/postings/4568</t>
         </is>
       </c>
       <c r="F69" s="2">
@@ -2436,7 +2436,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Residential Life Coordinator</t>
+          <t>Part-time Faculty Pool - Online Criminal Justice Instructor</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4568</t>
+          <t>https://jobs.sheridan.edu/postings/4086</t>
         </is>
       </c>
       <c r="F70" s="2">
@@ -2466,7 +2466,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Machine Tool Instructor</t>
+          <t>Part-time Faculty Pool - Culinary Instructor</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4471</t>
+          <t>https://jobs.sheridan.edu/postings/3690</t>
         </is>
       </c>
       <c r="F71" s="2">
@@ -2496,7 +2496,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Culinary Instructor</t>
+          <t>Vice President of Academic Affairs</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3690</t>
+          <t>https://jobs.sheridan.edu/postings/4686</t>
         </is>
       </c>
       <c r="F72" s="2">
@@ -2526,7 +2526,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Diesel Technology Instructor</t>
+          <t>Part-time Faculty Pool - Machine Tool Instructor</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4088</t>
+          <t>https://jobs.sheridan.edu/postings/4471</t>
         </is>
       </c>
       <c r="F73" s="2">
@@ -2586,7 +2586,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Computer Science or Information Technology Instructor</t>
+          <t>Part-time Faculty Pool - Diesel Technology Instructor</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4489</t>
+          <t>https://jobs.sheridan.edu/postings/4088</t>
         </is>
       </c>
       <c r="F75" s="2">
@@ -2646,7 +2646,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Theater Instructor</t>
+          <t>Part-time Faculty Pool - Computer Science or Information Technology Instructor</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4092</t>
+          <t>https://jobs.sheridan.edu/postings/4489</t>
         </is>
       </c>
       <c r="F77" s="2">
@@ -2706,7 +2706,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>(Student Position) Enrollment Services Assistant</t>
+          <t>Part-time Faculty Pool - Theater Instructor</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4500</t>
+          <t>https://jobs.sheridan.edu/postings/4092</t>
         </is>
       </c>
       <c r="F79" s="2">
@@ -2766,7 +2766,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>(Student Position) General’s Pantry Assistant</t>
+          <t>(Student Position) Enrollment Services Assistant</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4645</t>
+          <t>https://jobs.sheridan.edu/postings/4500</t>
         </is>
       </c>
       <c r="F81" s="2">
@@ -2826,7 +2826,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>(Student Position) WCA Gallery Assistant</t>
+          <t>(Student Position) General’s Pantry Assistant</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4507</t>
+          <t>https://jobs.sheridan.edu/postings/4645</t>
         </is>
       </c>
       <c r="F83" s="2">
@@ -2886,7 +2886,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>(Student Position) Sports &amp; Recreation Manager</t>
+          <t>(Student Position) WCA Gallery Assistant</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4649</t>
+          <t>https://jobs.sheridan.edu/postings/4507</t>
         </is>
       </c>
       <c r="F85" s="2">
@@ -2946,7 +2946,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>(Student Position) Grounds Maintenance Seasonal</t>
+          <t>(Student Position) Sports &amp; Recreation Manager</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4513</t>
+          <t>https://jobs.sheridan.edu/postings/4649</t>
         </is>
       </c>
       <c r="F87" s="2">
@@ -2976,7 +2976,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - HVAC Apprenticeship Instructor</t>
+          <t>(Student Position) Grounds Maintenance Seasonal</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3940</t>
+          <t>https://jobs.sheridan.edu/postings/4513</t>
         </is>
       </c>
       <c r="F88" s="2">
@@ -3006,7 +3006,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Administrative &amp; Work Based Learning Coordinator</t>
+          <t>Part-time Faculty Pool - HVAC Apprenticeship Instructor</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4656</t>
+          <t>https://jobs.sheridan.edu/postings/3940</t>
         </is>
       </c>
       <c r="F89" s="2">
@@ -3066,7 +3066,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>(Student Position) Financial Aid Office Assistant</t>
+          <t>Administrative &amp; Work Based Learning Coordinator</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4519</t>
+          <t>https://jobs.sheridan.edu/postings/4656</t>
         </is>
       </c>
       <c r="F91" s="2">
@@ -3096,7 +3096,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Health and Human Performance Instructor</t>
+          <t>(Student Position) Financial Aid Office Assistant</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3983</t>
+          <t>https://jobs.sheridan.edu/postings/4519</t>
         </is>
       </c>
       <c r="F92" s="2">
@@ -3126,7 +3126,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Dental Hygiene Instructor</t>
+          <t>Part-time Faculty Pool - Health and Human Performance Instructor</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/2847</t>
+          <t>https://jobs.sheridan.edu/postings/3983</t>
         </is>
       </c>
       <c r="F93" s="2">
@@ -3156,7 +3156,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Custodial Manager</t>
+          <t>Part-time Faculty Pool - Hospitality/Tourism</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4665</t>
+          <t>https://jobs.sheridan.edu/postings/4101</t>
         </is>
       </c>
       <c r="F94" s="2">
@@ -3186,7 +3186,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Hospitality/Tourism</t>
+          <t>Part-time Faculty Pool - Dental Hygiene Instructor</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4101</t>
+          <t>https://jobs.sheridan.edu/postings/2847</t>
         </is>
       </c>
       <c r="F95" s="2">
@@ -3216,7 +3216,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Massage Therapy Instructor</t>
+          <t>Custodial Manager</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4048</t>
+          <t>https://jobs.sheridan.edu/postings/4665</t>
         </is>
       </c>
       <c r="F96" s="2">
@@ -3276,7 +3276,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Anthropology Instructor (Online)</t>
+          <t>Part-time Faculty Pool - Massage Therapy Instructor</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2022-07-26</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3290</t>
+          <t>https://jobs.sheridan.edu/postings/4048</t>
         </is>
       </c>
       <c r="F98" s="2">
@@ -3366,7 +3366,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Human Services Instructor</t>
+          <t>Part-time Faculty Pool - Anthropology Instructor (Online)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2022-07-26</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4085</t>
+          <t>https://jobs.sheridan.edu/postings/3290</t>
         </is>
       </c>
       <c r="F101" s="2">
@@ -3426,7 +3426,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Nursing Instructor</t>
+          <t>Part-time Faculty Pool - Human Services Instructor</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2022-08-16</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/3326</t>
+          <t>https://jobs.sheridan.edu/postings/4085</t>
         </is>
       </c>
       <c r="F103" s="2">
@@ -3456,7 +3456,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Vice President of Academic Affairs</t>
+          <t>(Student Position) WCA Production Assistant</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4682</t>
+          <t>https://jobs.sheridan.edu/postings/4684</t>
         </is>
       </c>
       <c r="F104" s="2">
@@ -3516,7 +3516,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Psychology Instructor</t>
+          <t>Part-time Faculty Pool - Nursing Instructor</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2022-08-16</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4087</t>
+          <t>https://jobs.sheridan.edu/postings/3326</t>
         </is>
       </c>
       <c r="F106" s="2">
@@ -3576,7 +3576,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Commercial Motor Vehicle (CMV) Driver Training Instructor</t>
+          <t>Part-time Faculty Pool - Psychology Instructor</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4487</t>
+          <t>https://jobs.sheridan.edu/postings/4087</t>
         </is>
       </c>
       <c r="F108" s="2">
@@ -3636,7 +3636,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Part-time Faculty Pool - Education Instructor</t>
+          <t>Part-time Faculty Pool - Commercial Motor Vehicle (CMV) Driver Training Instructor</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4089</t>
+          <t>https://jobs.sheridan.edu/postings/4487</t>
         </is>
       </c>
       <c r="F110" s="2">
@@ -3696,7 +3696,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>(Student Position) Dental Hygiene Program Assistant</t>
+          <t>Part-time Faculty Pool - Education Instructor</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4497</t>
+          <t>https://jobs.sheridan.edu/postings/4089</t>
         </is>
       </c>
       <c r="F112" s="2">
@@ -3756,7 +3756,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>(Student Position) Campus Life &amp; Housing Office Assistant</t>
+          <t>(Student Position) Dental Hygiene Program Assistant</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4643</t>
+          <t>https://jobs.sheridan.edu/postings/4497</t>
         </is>
       </c>
       <c r="F114" s="2">
@@ -3816,7 +3816,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>(Student Position) Information Technology (IT) Night Helpdesk</t>
+          <t>(Student Position) Campus Life &amp; Housing Office Assistant</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://jobs.sheridan.edu/postings/4502</t>
+          <t>https://jobs.sheridan.edu/postings/4643</t>
         </is>
       </c>
       <c r="F116" s="2">
@@ -3876,27 +3876,27 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Facilities Director</t>
+          <t>(Student Position) Information Technology (IT) Night Helpdesk</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Northwest College Campus</t>
+          <t>Sheridan College Campus</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Northwest College</t>
+          <t>Sheridan College</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://northwestcollege.simplehire.com/postings/2640</t>
+          <t>https://jobs.sheridan.edu/postings/4502</t>
         </is>
       </c>
       <c r="F118" s="2">
@@ -3906,7 +3906,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Adjunct - Instructor of CAD</t>
+          <t>Facilities Director</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://northwestcollege.simplehire.com/postings/2671</t>
+          <t>https://northwestcollege.simplehire.com/postings/2640</t>
         </is>
       </c>
       <c r="F119" s="2">
@@ -3936,7 +3936,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Computing Services Analyst</t>
+          <t>Adjunct - Instructor of CAD</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://northwestcollege.simplehire.com/postings/2686</t>
+          <t>https://northwestcollege.simplehire.com/postings/2671</t>
         </is>
       </c>
       <c r="F120" s="2">
@@ -3966,7 +3966,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Counselor – Student Success Program Coordinator</t>
+          <t>Computing Services Analyst</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://northwestcollege.simplehire.com/postings/2693</t>
+          <t>https://northwestcollege.simplehire.com/postings/2686</t>
         </is>
       </c>
       <c r="F121" s="2">
@@ -3996,7 +3996,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Financial Aid Specialist</t>
+          <t>Counselor – Student Success Program Coordinator</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://northwestcollege.simplehire.com/postings/2670</t>
+          <t>https://northwestcollege.simplehire.com/postings/2693</t>
         </is>
       </c>
       <c r="F122" s="2">
@@ -4026,7 +4026,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Interim Educational Support Coordinator - Equine Program</t>
+          <t>Financial Aid Specialist</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://northwestcollege.simplehire.com/postings/2683</t>
+          <t>https://northwestcollege.simplehire.com/postings/2670</t>
         </is>
       </c>
       <c r="F123" s="2">
@@ -4056,7 +4056,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>FIxed Term Instructor of Equine Studies</t>
+          <t>Interim Educational Support Coordinator - Equine Program</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://northwestcollege.simplehire.com/postings/2691</t>
+          <t>https://northwestcollege.simplehire.com/postings/2683</t>
         </is>
       </c>
       <c r="F124" s="2">
@@ -4086,27 +4086,27 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>FIxed Term Instructor of Equine Studies</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Northwest College Campus</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>University of Wyoming</t>
+          <t>Northwest College</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://northwestcollege.simplehire.com/postings/2691</t>
         </is>
       </c>
       <c r="F125" s="2">
@@ -4116,12 +4116,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F126" s="2">
@@ -4146,7 +4146,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F127" s="2">
@@ -4176,7 +4176,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Assistant Professor - English</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261885</t>
         </is>
       </c>
       <c r="F128" s="2">
@@ -4206,7 +4206,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F129" s="2">
@@ -4236,7 +4236,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F130" s="2">
@@ -4266,7 +4266,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F131" s="2">
@@ -4296,7 +4296,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F132" s="2">
@@ -4326,7 +4326,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F133" s="2">
@@ -4356,7 +4356,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F134" s="2">
@@ -4386,7 +4386,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F135" s="2">
@@ -4416,7 +4416,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F136" s="2">
@@ -4446,7 +4446,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F137" s="2">
@@ -4476,7 +4476,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F138" s="2">
@@ -4506,7 +4506,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F139" s="2">
@@ -4536,7 +4536,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F140" s="2">
@@ -4566,7 +4566,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F141" s="2">
@@ -4596,7 +4596,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F142" s="2">
@@ -4626,7 +4626,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F143" s="2">
@@ -4656,7 +4656,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F144" s="2">
@@ -4686,7 +4686,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F145" s="2">
@@ -4716,7 +4716,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F146" s="2">
@@ -4746,7 +4746,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F147" s="2">
@@ -4776,7 +4776,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F148" s="2">
@@ -4806,7 +4806,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Archives Aide Expeditor</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F149" s="2">
@@ -4836,17 +4836,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Laramie, WY, United States</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
         </is>
       </c>
       <c r="F150" s="2">
@@ -4866,12 +4866,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F151" s="2">
@@ -4896,7 +4896,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F152" s="2">
@@ -4926,7 +4926,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Assistant Professor - English</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261885</t>
         </is>
       </c>
       <c r="F153" s="2">
@@ -4956,7 +4956,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F154" s="2">
@@ -4986,7 +4986,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F155" s="2">
@@ -5016,7 +5016,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F156" s="2">
@@ -5046,7 +5046,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F157" s="2">
@@ -5076,7 +5076,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F158" s="2">
@@ -5106,7 +5106,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F159" s="2">
@@ -5136,7 +5136,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F160" s="2">
@@ -5166,7 +5166,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F161" s="2">
@@ -5196,7 +5196,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F162" s="2">
@@ -5226,7 +5226,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F163" s="2">
@@ -5256,7 +5256,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F164" s="2">
@@ -5286,7 +5286,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F165" s="2">
@@ -5316,7 +5316,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F166" s="2">
@@ -5346,7 +5346,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F167" s="2">
@@ -5376,7 +5376,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F168" s="2">
@@ -5406,7 +5406,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F169" s="2">
@@ -5436,7 +5436,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F170" s="2">
@@ -5466,7 +5466,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F171" s="2">
@@ -5496,7 +5496,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F172" s="2">
@@ -5526,7 +5526,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F173" s="2">
@@ -5556,7 +5556,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Archives Aide Expeditor</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F174" s="2">
@@ -5586,17 +5586,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Laramie, WY, United States</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
         </is>
       </c>
       <c r="F175" s="2">
@@ -5616,12 +5616,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F176" s="2">
@@ -5646,7 +5646,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F177" s="2">
@@ -5676,7 +5676,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Assistant Professor - English</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261885</t>
         </is>
       </c>
       <c r="F178" s="2">
@@ -5706,7 +5706,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F179" s="2">
@@ -5736,7 +5736,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F180" s="2">
@@ -5766,7 +5766,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F181" s="2">
@@ -5796,7 +5796,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F182" s="2">
@@ -5826,7 +5826,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F183" s="2">
@@ -5856,7 +5856,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F184" s="2">
@@ -5886,7 +5886,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F185" s="2">
@@ -5916,7 +5916,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F186" s="2">
@@ -5946,7 +5946,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F187" s="2">
@@ -5976,7 +5976,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F188" s="2">
@@ -6006,7 +6006,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F189" s="2">
@@ -6036,7 +6036,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F190" s="2">
@@ -6066,7 +6066,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F191" s="2">
@@ -6096,7 +6096,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F192" s="2">
@@ -6126,7 +6126,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F193" s="2">
@@ -6156,7 +6156,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F194" s="2">
@@ -6186,7 +6186,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F195" s="2">
@@ -6216,7 +6216,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F196" s="2">
@@ -6246,7 +6246,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F197" s="2">
@@ -6276,7 +6276,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F198" s="2">
@@ -6306,7 +6306,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Archives Aide Expeditor</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F199" s="2">
@@ -6336,17 +6336,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Laramie, WY, United States</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
         </is>
       </c>
       <c r="F200" s="2">
@@ -6366,12 +6366,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F201" s="2">
@@ -6396,7 +6396,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F202" s="2">
@@ -6426,7 +6426,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Assistant Professor - English</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261885</t>
         </is>
       </c>
       <c r="F203" s="2">
@@ -6456,7 +6456,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F204" s="2">
@@ -6486,7 +6486,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F205" s="2">
@@ -6516,7 +6516,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F206" s="2">
@@ -6546,7 +6546,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F207" s="2">
@@ -6576,7 +6576,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F208" s="2">
@@ -6606,7 +6606,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F209" s="2">
@@ -6636,7 +6636,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F210" s="2">
@@ -6666,7 +6666,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F211" s="2">
@@ -6696,7 +6696,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F212" s="2">
@@ -6726,7 +6726,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F213" s="2">
@@ -6756,7 +6756,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F214" s="2">
@@ -6786,7 +6786,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F215" s="2">
@@ -6816,7 +6816,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F216" s="2">
@@ -6846,7 +6846,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F217" s="2">
@@ -6876,7 +6876,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F218" s="2">
@@ -6906,7 +6906,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F219" s="2">
@@ -6936,7 +6936,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F220" s="2">
@@ -6966,7 +6966,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F221" s="2">
@@ -6996,7 +6996,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F222" s="2">
@@ -7026,7 +7026,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F223" s="2">
@@ -7056,7 +7056,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Archives Aide Expeditor</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F224" s="2">
@@ -7086,17 +7086,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Laramie, WY, United States</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
         </is>
       </c>
       <c r="F225" s="2">
@@ -7116,12 +7116,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F226" s="2">
@@ -7146,7 +7146,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F227" s="2">
@@ -7176,7 +7176,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Assistant Professor - English</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261885</t>
         </is>
       </c>
       <c r="F228" s="2">
@@ -7206,7 +7206,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F229" s="2">
@@ -7236,7 +7236,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F230" s="2">
@@ -7266,7 +7266,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F231" s="2">
@@ -7296,7 +7296,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F232" s="2">
@@ -7326,7 +7326,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F233" s="2">
@@ -7356,7 +7356,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F234" s="2">
@@ -7386,7 +7386,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F235" s="2">
@@ -7416,7 +7416,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F236" s="2">
@@ -7446,7 +7446,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F237" s="2">
@@ -7476,7 +7476,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F238" s="2">
@@ -7506,7 +7506,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F239" s="2">
@@ -7536,7 +7536,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F240" s="2">
@@ -7566,7 +7566,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F241" s="2">
@@ -7596,7 +7596,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F242" s="2">
@@ -7626,7 +7626,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F243" s="2">
@@ -7656,7 +7656,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F244" s="2">
@@ -7686,7 +7686,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F245" s="2">
@@ -7716,7 +7716,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F246" s="2">
@@ -7746,7 +7746,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F247" s="2">
@@ -7776,7 +7776,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F248" s="2">
@@ -7806,7 +7806,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Archives Aide Expeditor</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F249" s="2">
@@ -7836,17 +7836,17 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Laramie, WY, United States</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
         </is>
       </c>
       <c r="F250" s="2">
@@ -7866,12 +7866,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F251" s="2">
@@ -7896,7 +7896,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F252" s="2">
@@ -7926,7 +7926,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Assistant Professor - English</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261885</t>
         </is>
       </c>
       <c r="F253" s="2">
@@ -7956,7 +7956,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F254" s="2">
@@ -7986,7 +7986,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F255" s="2">
@@ -8016,7 +8016,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F256" s="2">
@@ -8046,7 +8046,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F257" s="2">
@@ -8076,7 +8076,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F258" s="2">
@@ -8106,7 +8106,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F259" s="2">
@@ -8136,7 +8136,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F260" s="2">
@@ -8166,7 +8166,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F261" s="2">
@@ -8196,7 +8196,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F262" s="2">
@@ -8226,7 +8226,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F263" s="2">
@@ -8256,7 +8256,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F264" s="2">
@@ -8286,7 +8286,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F265" s="2">
@@ -8316,7 +8316,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F266" s="2">
@@ -8346,7 +8346,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F267" s="2">
@@ -8376,7 +8376,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F268" s="2">
@@ -8406,7 +8406,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F269" s="2">
@@ -8436,7 +8436,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F270" s="2">
@@ -8466,7 +8466,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F271" s="2">
@@ -8496,7 +8496,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F272" s="2">
@@ -8526,7 +8526,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F273" s="2">
@@ -8556,7 +8556,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Archives Aide Expeditor</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F274" s="2">
@@ -8586,17 +8586,17 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Laramie, WY, United States</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
         </is>
       </c>
       <c r="F275" s="2">
@@ -8616,12 +8616,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F276" s="2">
@@ -8646,7 +8646,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F277" s="2">
@@ -8676,7 +8676,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Assistant Professor - English</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261885</t>
         </is>
       </c>
       <c r="F278" s="2">
@@ -8706,7 +8706,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F279" s="2">
@@ -8736,7 +8736,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F280" s="2">
@@ -8766,7 +8766,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F281" s="2">
@@ -8796,7 +8796,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F282" s="2">
@@ -8826,7 +8826,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F283" s="2">
@@ -8856,7 +8856,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F284" s="2">
@@ -8886,7 +8886,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F285" s="2">
@@ -8916,7 +8916,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F286" s="2">
@@ -8946,7 +8946,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F287" s="2">
@@ -8976,7 +8976,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F288" s="2">
@@ -9006,7 +9006,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F289" s="2">
@@ -9036,7 +9036,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F290" s="2">
@@ -9066,7 +9066,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F291" s="2">
@@ -9096,7 +9096,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F292" s="2">
@@ -9126,7 +9126,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F293" s="2">
@@ -9156,7 +9156,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F294" s="2">
@@ -9186,7 +9186,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F295" s="2">
@@ -9216,7 +9216,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F296" s="2">
@@ -9246,7 +9246,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F297" s="2">
@@ -9276,7 +9276,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F298" s="2">
@@ -9306,7 +9306,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Archives Aide Expeditor</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F299" s="2">
@@ -9336,17 +9336,17 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Laramie, WY, United States</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
         </is>
       </c>
       <c r="F300" s="2">
@@ -9366,12 +9366,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F301" s="2">
@@ -9396,7 +9396,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F302" s="2">
@@ -9426,7 +9426,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Assistant Professor - English</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261885</t>
         </is>
       </c>
       <c r="F303" s="2">
@@ -9456,7 +9456,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F304" s="2">
@@ -9486,7 +9486,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F305" s="2">
@@ -9516,7 +9516,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F306" s="2">
@@ -9546,7 +9546,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F307" s="2">
@@ -9576,7 +9576,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F308" s="2">
@@ -9606,7 +9606,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -9626,7 +9626,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F309" s="2">
@@ -9636,7 +9636,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F310" s="2">
@@ -9666,7 +9666,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F311" s="2">
@@ -9696,7 +9696,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F312" s="2">
@@ -9726,7 +9726,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F313" s="2">
@@ -9756,7 +9756,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -9776,7 +9776,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F314" s="2">
@@ -9786,7 +9786,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F315" s="2">
@@ -9816,7 +9816,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F316" s="2">
@@ -9846,7 +9846,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F317" s="2">
@@ -9876,7 +9876,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F318" s="2">
@@ -9906,7 +9906,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F319" s="2">
@@ -9936,7 +9936,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F320" s="2">
@@ -9966,7 +9966,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -9976,7 +9976,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F321" s="2">
@@ -9996,7 +9996,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F322" s="2">
@@ -10026,7 +10026,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F323" s="2">
@@ -10056,7 +10056,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Archives Aide Expeditor</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F324" s="2">
@@ -10086,17 +10086,17 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Laramie, WY, United States</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
         </is>
       </c>
       <c r="F325" s="2">
@@ -10116,12 +10116,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
+          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Laramie, WY, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
         </is>
       </c>
       <c r="F326" s="2">
@@ -10146,7 +10146,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
+          <t>Preventive Mt Technician - Preventive Maintenance</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
         </is>
       </c>
       <c r="F327" s="2">
@@ -10176,7 +10176,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
+          <t>Assistant Professor - English</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261885</t>
         </is>
       </c>
       <c r="F328" s="2">
@@ -10206,7 +10206,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
+          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
         </is>
       </c>
       <c r="F329" s="2">
@@ -10236,7 +10236,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
+          <t>Hourly Pooled - Digital Engagement Intern</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
         </is>
       </c>
       <c r="F330" s="2">
@@ -10266,7 +10266,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
+          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
         </is>
       </c>
       <c r="F331" s="2">
@@ -10296,7 +10296,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
+          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
         </is>
       </c>
       <c r="F332" s="2">
@@ -10326,7 +10326,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
+          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -10346,7 +10346,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
         </is>
       </c>
       <c r="F333" s="2">
@@ -10356,7 +10356,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
+          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
         </is>
       </c>
       <c r="F334" s="2">
@@ -10386,7 +10386,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Director, Creative Media-Football</t>
+          <t>Heavy Equipment Operator - Equipment Services</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
         </is>
       </c>
       <c r="F335" s="2">
@@ -10416,7 +10416,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Program Coordinator, Senior - Science Institute</t>
+          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
         </is>
       </c>
       <c r="F336" s="2">
@@ -10446,7 +10446,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
+          <t>Director, Creative Media-Football</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
         </is>
       </c>
       <c r="F337" s="2">
@@ -10476,7 +10476,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
+          <t>Program Coordinator, Senior - Science Institute</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261806</t>
         </is>
       </c>
       <c r="F338" s="2">
@@ -10506,7 +10506,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
+          <t>Hourly Pooled - Culinary Assistant, N. Hall Dining Center</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261838</t>
         </is>
       </c>
       <c r="F339" s="2">
@@ -10536,7 +10536,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
+          <t>Work Study Posn Student - Farm and Ranch Worker, Rodeo</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261813</t>
         </is>
       </c>
       <c r="F340" s="2">
@@ -10566,7 +10566,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
+          <t>Work Study - Campus Recreation, Intramural Sports Official</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261843</t>
         </is>
       </c>
       <c r="F341" s="2">
@@ -10596,7 +10596,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
+          <t>Work Study - Campus Recreation, Business Office Student Staff</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261844</t>
         </is>
       </c>
       <c r="F342" s="2">
@@ -10626,7 +10626,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Office Associate - Psychology Center</t>
+          <t>Office Associate - CRMJ and SPPAIS (Politics Public Affairs &amp; International Studies)</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -10646,7 +10646,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261878</t>
         </is>
       </c>
       <c r="F343" s="2">
@@ -10656,7 +10656,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
+          <t>Hourly Pooled - Campus Recreation - Graphic Design and Photography</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261877</t>
         </is>
       </c>
       <c r="F344" s="2">
@@ -10686,7 +10686,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
+          <t>Office Associate - Psychology Center</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -10696,7 +10696,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261873</t>
         </is>
       </c>
       <c r="F345" s="2">
@@ -10716,7 +10716,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
+          <t>Primary Care Physician/Athletics Medical Director - Sports Medicine</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261874</t>
         </is>
       </c>
       <c r="F346" s="2">
@@ -10746,7 +10746,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
+          <t>Hourly Pooled - Marketing &amp; Communications Student Intern</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261899</t>
         </is>
       </c>
       <c r="F347" s="2">
@@ -10776,7 +10776,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+          <t>Hourly Pooled - ASUW Deputy Office Associate</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261904</t>
         </is>
       </c>
       <c r="F348" s="2">
@@ -10806,7 +10806,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Hourly Pooled - Archives Aide Expeditor</t>
+          <t>Hourly Pooled - Curatorial Internship: Gerald and Joyce Lang Print Study Room, University Art Museum</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -10826,10 +10826,40 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261910</t>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261903</t>
         </is>
       </c>
       <c r="F349" s="2">
+        <v>46237</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Hourly Pooled - Broadcast Studio Manager, Student Media</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Laramie, WY, United States</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>University of Wyoming</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261912</t>
+        </is>
+      </c>
+      <c r="F350" s="2">
         <v>46237</v>
       </c>
     </row>

--- a/Wy_Ed_Jobs/hedata.xlsx
+++ b/Wy_Ed_Jobs/hedata.xlsx
@@ -697,6 +697,15 @@
     <t>https://wwcwy.peopleadmin.com/postings/5952</t>
   </si>
   <si>
+    <t>Workforce Development and Community Education Office Assistant (Part Time Benefited)</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>https://wwcwy.peopleadmin.com/postings/6007</t>
+  </si>
+  <si>
     <t>Instructor/Assistant Professor of Powerline Technology</t>
   </si>
   <si>
@@ -706,15 +715,6 @@
     <t>https://wwcwy.peopleadmin.com/postings/5859</t>
   </si>
   <si>
-    <t>Workforce Development and Community Education Office Assistant (Part Time Benefited)</t>
-  </si>
-  <si>
-    <t>2026-08-04</t>
-  </si>
-  <si>
-    <t>https://wwcwy.peopleadmin.com/postings/6007</t>
-  </si>
-  <si>
     <t>Physics Student Worker (lab) (S. Schutten)</t>
   </si>
   <si>
@@ -733,6 +733,15 @@
     <t>https://wwcwy.peopleadmin.com/postings/5876</t>
   </si>
   <si>
+    <t>Instructor/Assistant Professor of Information Systems</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>https://wwcwy.peopleadmin.com/postings/5974</t>
+  </si>
+  <si>
     <t>Adjunct Faculty - Industrial Safety</t>
   </si>
   <si>
@@ -742,15 +751,6 @@
     <t>https://wwcwy.peopleadmin.com/postings/5258</t>
   </si>
   <si>
-    <t>Instructor/Assistant Professor of Information Systems</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>https://wwcwy.peopleadmin.com/postings/5974</t>
-  </si>
-  <si>
     <t>Adjunct Faculty - Physics</t>
   </si>
   <si>
@@ -784,6 +784,15 @@
     <t>https://wwcwy.peopleadmin.com/postings/5918</t>
   </si>
   <si>
+    <t>Adjunct Faculty - Certified Nursing Assistant (CNA) (Rock Springs &amp; Evanston)</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>https://wwcwy.peopleadmin.com/postings/5503</t>
+  </si>
+  <si>
     <t>IT Support Technician</t>
   </si>
   <si>
@@ -793,15 +802,6 @@
     <t>https://wwcwy.peopleadmin.com/postings/5984</t>
   </si>
   <si>
-    <t>Adjunct Faculty - Certified Nursing Assistant (CNA) (Rock Springs &amp; Evanston)</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>https://wwcwy.peopleadmin.com/postings/5503</t>
-  </si>
-  <si>
     <t>Adjunct Faculty - Business</t>
   </si>
   <si>
@@ -811,6 +811,15 @@
     <t>https://wwcwy.peopleadmin.com/postings/5933</t>
   </si>
   <si>
+    <t>Adjunct Faculty- Physical or Outdoor Activity</t>
+  </si>
+  <si>
+    <t>2025-06-17</t>
+  </si>
+  <si>
+    <t>https://wwcwy.peopleadmin.com/postings/5601</t>
+  </si>
+  <si>
     <t>Children's Center Part-Time Aide (Substitute)</t>
   </si>
   <si>
@@ -820,15 +829,6 @@
     <t>https://wwcwy.peopleadmin.com/postings/5990</t>
   </si>
   <si>
-    <t>Adjunct Faculty- Physical or Outdoor Activity</t>
-  </si>
-  <si>
-    <t>2025-06-17</t>
-  </si>
-  <si>
-    <t>https://wwcwy.peopleadmin.com/postings/5601</t>
-  </si>
-  <si>
     <t>Instructor/Assistant Professor of Electrical &amp; Instrumentation (Rock Springs Campus)</t>
   </si>
   <si>
@@ -838,6 +838,15 @@
     <t>https://wwcwy.peopleadmin.com/postings/5940</t>
   </si>
   <si>
+    <t>Bus Drivers - Part Time</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>https://wwcwy.peopleadmin.com/postings/5718</t>
+  </si>
+  <si>
     <t>Adjunct Faculty - Nutrition</t>
   </si>
   <si>
@@ -847,15 +856,6 @@
     <t>https://wwcwy.peopleadmin.com/postings/5995</t>
   </si>
   <si>
-    <t>Bus Drivers - Part Time</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>https://wwcwy.peopleadmin.com/postings/5718</t>
-  </si>
-  <si>
     <t>Multimedia Student Worker (Fall 2026)</t>
   </si>
   <si>
@@ -865,6 +865,15 @@
     <t>https://wwcwy.peopleadmin.com/postings/5946</t>
   </si>
   <si>
+    <t>Adjunct Faculty - Biology</t>
+  </si>
+  <si>
+    <t>2025-12-11</t>
+  </si>
+  <si>
+    <t>https://wwcwy.peopleadmin.com/postings/5805</t>
+  </si>
+  <si>
     <t>Adjunct Faculty - Medical Term</t>
   </si>
   <si>
@@ -874,21 +883,21 @@
     <t>https://wwcwy.peopleadmin.com/postings/5999</t>
   </si>
   <si>
-    <t>Adjunct Faculty - Biology</t>
-  </si>
-  <si>
-    <t>2025-12-11</t>
-  </si>
-  <si>
-    <t>https://wwcwy.peopleadmin.com/postings/5805</t>
-  </si>
-  <si>
     <t>MAVERICK The Mascot Student Worker (Fall 2026)</t>
   </si>
   <si>
     <t>https://wwcwy.peopleadmin.com/postings/5950</t>
   </si>
   <si>
+    <t>Director of Workforce Development and the Green River Center</t>
+  </si>
+  <si>
+    <t>2025-12-17</t>
+  </si>
+  <si>
+    <t>https://wwcwy.peopleadmin.com/postings/5818</t>
+  </si>
+  <si>
     <t>Student Library Aide</t>
   </si>
   <si>
@@ -898,15 +907,6 @@
     <t>https://wwcwy.peopleadmin.com/postings/6005</t>
   </si>
   <si>
-    <t>Director of Workforce Development and the Green River Center</t>
-  </si>
-  <si>
-    <t>2025-12-17</t>
-  </si>
-  <si>
-    <t>https://wwcwy.peopleadmin.com/postings/5818</t>
-  </si>
-  <si>
     <t>Fitness Center - Student Worker</t>
   </si>
   <si>
@@ -937,21 +937,21 @@
     <t>https://wwcwy.peopleadmin.com/postings/5877</t>
   </si>
   <si>
+    <t>Musical Theatre Director (Seasonal Assignment)</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>https://wwcwy.peopleadmin.com/postings/5976</t>
+  </si>
+  <si>
     <t>Adjunct Faculty-Commerical Driver's License (CDL)</t>
   </si>
   <si>
     <t>https://wwcwy.peopleadmin.com/postings/5262</t>
   </si>
   <si>
-    <t>Musical Theatre Director (Seasonal Assignment)</t>
-  </si>
-  <si>
-    <t>2026-06-03</t>
-  </si>
-  <si>
-    <t>https://wwcwy.peopleadmin.com/postings/5976</t>
-  </si>
-  <si>
     <t>Workforce MSHA Instructor</t>
   </si>
   <si>
@@ -985,6 +985,15 @@
     <t>https://wwcwy.peopleadmin.com/postings/5926</t>
   </si>
   <si>
+    <t>Instructor/Assistant Professor of Industrial Maintenance</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>https://wwcwy.peopleadmin.com/postings/5552</t>
+  </si>
+  <si>
     <t>Systems Administrator</t>
   </si>
   <si>
@@ -994,15 +1003,6 @@
     <t>https://wwcwy.peopleadmin.com/postings/5986</t>
   </si>
   <si>
-    <t>Instructor/Assistant Professor of Industrial Maintenance</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>https://wwcwy.peopleadmin.com/postings/5552</t>
-  </si>
-  <si>
     <t>Adjunct Faculty - Geology</t>
   </si>
   <si>
@@ -1012,6 +1012,12 @@
     <t>https://wwcwy.peopleadmin.com/postings/5938</t>
   </si>
   <si>
+    <t>INBRE Research Technicians</t>
+  </si>
+  <si>
+    <t>https://wwcwy.peopleadmin.com/postings/5716</t>
+  </si>
+  <si>
     <t>Accounting Technician</t>
   </si>
   <si>
@@ -1021,36 +1027,39 @@
     <t>https://wwcwy.peopleadmin.com/postings/5991</t>
   </si>
   <si>
-    <t>INBRE Research Technicians</t>
-  </si>
-  <si>
-    <t>https://wwcwy.peopleadmin.com/postings/5716</t>
-  </si>
-  <si>
     <t>Print Shop Student Worker (Fall 2026)</t>
   </si>
   <si>
     <t>https://wwcwy.peopleadmin.com/postings/5944</t>
   </si>
   <si>
+    <t>Lifeguard 2025-2026</t>
+  </si>
+  <si>
+    <t>https://wwcwy.peopleadmin.com/postings/5719</t>
+  </si>
+  <si>
     <t>Adjunct Faculty - Information Systems</t>
   </si>
   <si>
     <t>https://wwcwy.peopleadmin.com/postings/5997</t>
   </si>
   <si>
-    <t>Lifeguard 2025-2026</t>
-  </si>
-  <si>
-    <t>https://wwcwy.peopleadmin.com/postings/5719</t>
-  </si>
-  <si>
     <t>President's Social Media Student Worker (Fall 2026)</t>
   </si>
   <si>
     <t>https://wwcwy.peopleadmin.com/postings/5948</t>
   </si>
   <si>
+    <t>Adjunct Faculty - History</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>https://wwcwy.peopleadmin.com/postings/5809</t>
+  </si>
+  <si>
     <t>Admissions Counselor</t>
   </si>
   <si>
@@ -1060,15 +1069,6 @@
     <t>https://wwcwy.peopleadmin.com/postings/6003</t>
   </si>
   <si>
-    <t>Adjunct Faculty - History</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>https://wwcwy.peopleadmin.com/postings/5809</t>
-  </si>
-  <si>
     <t>Adjunct</t>
   </si>
   <si>
@@ -1429,6 +1429,12 @@
     <t>https://jobs.sheridan.edu/postings/4511</t>
   </si>
   <si>
+    <t>Part-time Faculty Pool - Composites Manufacturing</t>
+  </si>
+  <si>
+    <t>https://jobs.sheridan.edu/postings/4097</t>
+  </si>
+  <si>
     <t>Hospitality Faculty Coordinator</t>
   </si>
   <si>
@@ -1438,12 +1444,6 @@
     <t>https://jobs.sheridan.edu/postings/4660</t>
   </si>
   <si>
-    <t>Part-time Faculty Pool - Composites Manufacturing</t>
-  </si>
-  <si>
-    <t>https://jobs.sheridan.edu/postings/4097</t>
-  </si>
-  <si>
     <t>Part-time Academic Support Services Pool- Academic Support Tutor</t>
   </si>
   <si>
@@ -1519,6 +1519,12 @@
     <t>https://jobs.sheridan.edu/postings/4684</t>
   </si>
   <si>
+    <t>(Student Position) Box Office Assistant</t>
+  </si>
+  <si>
+    <t>https://jobs.sheridan.edu/postings/4560</t>
+  </si>
+  <si>
     <t>Part-time Faculty Pool - Community Interest (CI) Johnson County</t>
   </si>
   <si>
@@ -1528,12 +1534,6 @@
     <t>https://jobs.sheridan.edu/postings/4084</t>
   </si>
   <si>
-    <t>(Student Position) Box Office Assistant</t>
-  </si>
-  <si>
-    <t>https://jobs.sheridan.edu/postings/4560</t>
-  </si>
-  <si>
     <t>Part-time Faculty Pool - Electrical Apprenticeship Instructor</t>
   </si>
   <si>
@@ -1636,18 +1636,18 @@
     <t>https://jobs.sheridan.edu/postings/4092</t>
   </si>
   <si>
+    <t>Part-time Faculty Pool - Accounting Instructor</t>
+  </si>
+  <si>
+    <t>https://jobs.sheridan.edu/postings/3763</t>
+  </si>
+  <si>
     <t>(Student Position) Enrollment Services Assistant</t>
   </si>
   <si>
     <t>https://jobs.sheridan.edu/postings/4500</t>
   </si>
   <si>
-    <t>Part-time Faculty Pool - Accounting Instructor</t>
-  </si>
-  <si>
-    <t>https://jobs.sheridan.edu/postings/3763</t>
-  </si>
-  <si>
     <t>(Student Position) Sports &amp; Recreation Manager</t>
   </si>
   <si>
@@ -1744,6 +1744,12 @@
     <t>https://jobs.sheridan.edu/postings/4681</t>
   </si>
   <si>
+    <t>(Student Position) Peer Tutor</t>
+  </si>
+  <si>
+    <t>https://jobs.sheridan.edu/postings/4523</t>
+  </si>
+  <si>
     <t>Part-time Faculty Pool - Massage Therapy Instructor</t>
   </si>
   <si>
@@ -1753,12 +1759,6 @@
     <t>https://jobs.sheridan.edu/postings/4048</t>
   </si>
   <si>
-    <t>(Student Position) Peer Tutor</t>
-  </si>
-  <si>
-    <t>https://jobs.sheridan.edu/postings/4523</t>
-  </si>
-  <si>
     <t>Part-time Faculty Pool - Engineering Science and Engineering Tech Instructor</t>
   </si>
   <si>
@@ -1858,18 +1858,18 @@
     <t>https://jobs.sheridan.edu/postings/4089</t>
   </si>
   <si>
+    <t>Part-time Faculty Pool - Business Instructor</t>
+  </si>
+  <si>
+    <t>https://jobs.sheridan.edu/postings/3760</t>
+  </si>
+  <si>
     <t>(Student Position) Dental Hygiene Program Assistant</t>
   </si>
   <si>
     <t>https://jobs.sheridan.edu/postings/4497</t>
   </si>
   <si>
-    <t>Part-time Faculty Pool - Business Instructor</t>
-  </si>
-  <si>
-    <t>https://jobs.sheridan.edu/postings/3760</t>
-  </si>
-  <si>
     <t>(Student Position) Sports and Recreation Assistant</t>
   </si>
   <si>
@@ -1954,18 +1954,24 @@
     <t>https://northwestcollege.simplehire.com/postings/2693</t>
   </si>
   <si>
+    <t>Engineer, Senior - Facilities Engineering</t>
+  </si>
+  <si>
+    <t>Laramie, WY, United States</t>
+  </si>
+  <si>
+    <t>University of Wyoming</t>
+  </si>
+  <si>
+    <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261770</t>
+  </si>
+  <si>
     <t>Hourly Pooled - Research Assistant, Ecosystem Science &amp; Management</t>
   </si>
   <si>
-    <t>Laramie, WY, United States</t>
-  </si>
-  <si>
     <t>2026-08-10</t>
   </si>
   <si>
-    <t>University of Wyoming</t>
-  </si>
-  <si>
     <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262095</t>
   </si>
   <si>
@@ -2117,12 +2123,6 @@
   </si>
   <si>
     <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261885</t>
-  </si>
-  <si>
-    <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
-  </si>
-  <si>
-    <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
   </si>
 </sst>
 </file>
@@ -5103,13 +5103,13 @@
         <v>223</v>
       </c>
       <c r="C132" t="s">
-        <v>240</v>
+        <v>308</v>
       </c>
       <c r="D132" t="s">
         <v>225</v>
       </c>
       <c r="E132" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F132" s="1">
         <v>46245</v>
@@ -5117,13 +5117,13 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B133" t="s">
         <v>223</v>
       </c>
       <c r="C133" t="s">
-        <v>310</v>
+        <v>243</v>
       </c>
       <c r="D133" t="s">
         <v>225</v>
@@ -5163,7 +5163,7 @@
         <v>223</v>
       </c>
       <c r="C135" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D135" t="s">
         <v>225</v>
@@ -5283,13 +5283,13 @@
         <v>223</v>
       </c>
       <c r="C141" t="s">
-        <v>333</v>
+        <v>275</v>
       </c>
       <c r="D141" t="s">
         <v>225</v>
       </c>
       <c r="E141" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F141" s="1">
         <v>46245</v>
@@ -5297,13 +5297,13 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B142" t="s">
         <v>223</v>
       </c>
       <c r="C142" t="s">
-        <v>278</v>
+        <v>335</v>
       </c>
       <c r="D142" t="s">
         <v>225</v>
@@ -5343,7 +5343,7 @@
         <v>223</v>
       </c>
       <c r="C144" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="D144" t="s">
         <v>225</v>
@@ -5363,7 +5363,7 @@
         <v>223</v>
       </c>
       <c r="C145" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="D145" t="s">
         <v>225</v>
@@ -5763,7 +5763,7 @@
         <v>382</v>
       </c>
       <c r="C165" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D165" t="s">
         <v>384</v>
@@ -6443,13 +6443,13 @@
         <v>458</v>
       </c>
       <c r="C199" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="D199" t="s">
         <v>460</v>
       </c>
       <c r="E199" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F199" s="1">
         <v>46245</v>
@@ -6457,13 +6457,13 @@
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B200" t="s">
         <v>458</v>
       </c>
       <c r="C200" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="D200" t="s">
         <v>460</v>
@@ -6683,13 +6683,13 @@
         <v>458</v>
       </c>
       <c r="C211" t="s">
-        <v>502</v>
+        <v>234</v>
       </c>
       <c r="D211" t="s">
         <v>460</v>
       </c>
       <c r="E211" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F211" s="1">
         <v>46245</v>
@@ -6697,13 +6697,13 @@
     </row>
     <row r="212" spans="1:6">
       <c r="A212" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B212" t="s">
         <v>458</v>
       </c>
       <c r="C212" t="s">
-        <v>234</v>
+        <v>504</v>
       </c>
       <c r="D212" t="s">
         <v>460</v>
@@ -6883,7 +6883,7 @@
         <v>458</v>
       </c>
       <c r="C221" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D221" t="s">
         <v>460</v>
@@ -6923,7 +6923,7 @@
         <v>458</v>
       </c>
       <c r="C223" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D223" t="s">
         <v>460</v>
@@ -6963,7 +6963,7 @@
         <v>458</v>
       </c>
       <c r="C225" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D225" t="s">
         <v>460</v>
@@ -7003,7 +7003,7 @@
         <v>458</v>
       </c>
       <c r="C227" t="s">
-        <v>469</v>
+        <v>534</v>
       </c>
       <c r="D227" t="s">
         <v>460</v>
@@ -7023,7 +7023,7 @@
         <v>458</v>
       </c>
       <c r="C228" t="s">
-        <v>534</v>
+        <v>469</v>
       </c>
       <c r="D228" t="s">
         <v>460</v>
@@ -7223,7 +7223,7 @@
         <v>458</v>
       </c>
       <c r="C238" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D238" t="s">
         <v>460</v>
@@ -7343,13 +7343,13 @@
         <v>458</v>
       </c>
       <c r="C244" t="s">
-        <v>577</v>
+        <v>492</v>
       </c>
       <c r="D244" t="s">
         <v>460</v>
       </c>
       <c r="E244" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="F244" s="1">
         <v>46245</v>
@@ -7357,13 +7357,13 @@
     </row>
     <row r="245" spans="1:6">
       <c r="A245" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B245" t="s">
         <v>458</v>
       </c>
       <c r="C245" t="s">
-        <v>492</v>
+        <v>579</v>
       </c>
       <c r="D245" t="s">
         <v>460</v>
@@ -7423,7 +7423,7 @@
         <v>458</v>
       </c>
       <c r="C248" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D248" t="s">
         <v>460</v>
@@ -7623,7 +7623,7 @@
         <v>458</v>
       </c>
       <c r="C258" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D258" t="s">
         <v>460</v>
@@ -7663,7 +7663,7 @@
         <v>458</v>
       </c>
       <c r="C260" t="s">
-        <v>469</v>
+        <v>534</v>
       </c>
       <c r="D260" t="s">
         <v>460</v>
@@ -7683,7 +7683,7 @@
         <v>458</v>
       </c>
       <c r="C261" t="s">
-        <v>534</v>
+        <v>469</v>
       </c>
       <c r="D261" t="s">
         <v>460</v>
@@ -7703,7 +7703,7 @@
         <v>458</v>
       </c>
       <c r="C262" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D262" t="s">
         <v>460</v>
@@ -7803,7 +7803,7 @@
         <v>628</v>
       </c>
       <c r="C267" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D267" t="s">
         <v>630</v>
@@ -7863,7 +7863,7 @@
         <v>628</v>
       </c>
       <c r="C270" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D270" t="s">
         <v>630</v>
@@ -7883,7 +7883,7 @@
         <v>628</v>
       </c>
       <c r="C271" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D271" t="s">
         <v>630</v>
@@ -7903,7 +7903,7 @@
         <v>628</v>
       </c>
       <c r="C272" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D272" t="s">
         <v>630</v>
@@ -7923,13 +7923,13 @@
         <v>647</v>
       </c>
       <c r="C273" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="D273" t="s">
+        <v>648</v>
+      </c>
+      <c r="E273" t="s">
         <v>649</v>
-      </c>
-      <c r="E273" t="s">
-        <v>650</v>
       </c>
       <c r="F273" s="1">
         <v>46245</v>
@@ -7937,16 +7937,16 @@
     </row>
     <row r="274" spans="1:6">
       <c r="A274" t="s">
+        <v>650</v>
+      </c>
+      <c r="B274" t="s">
+        <v>647</v>
+      </c>
+      <c r="C274" t="s">
         <v>651</v>
       </c>
-      <c r="B274" t="s">
-        <v>647</v>
-      </c>
-      <c r="C274" t="s">
-        <v>648</v>
-      </c>
       <c r="D274" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E274" t="s">
         <v>652</v>
@@ -7963,10 +7963,10 @@
         <v>647</v>
       </c>
       <c r="C275" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D275" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E275" t="s">
         <v>654</v>
@@ -7983,10 +7983,10 @@
         <v>647</v>
       </c>
       <c r="C276" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D276" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E276" t="s">
         <v>656</v>
@@ -8003,10 +8003,10 @@
         <v>647</v>
       </c>
       <c r="C277" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D277" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E277" t="s">
         <v>658</v>
@@ -8023,13 +8023,13 @@
         <v>647</v>
       </c>
       <c r="C278" t="s">
+        <v>651</v>
+      </c>
+      <c r="D278" t="s">
+        <v>648</v>
+      </c>
+      <c r="E278" t="s">
         <v>660</v>
-      </c>
-      <c r="D278" t="s">
-        <v>649</v>
-      </c>
-      <c r="E278" t="s">
-        <v>661</v>
       </c>
       <c r="F278" s="1">
         <v>46245</v>
@@ -8037,16 +8037,16 @@
     </row>
     <row r="279" spans="1:6">
       <c r="A279" t="s">
+        <v>661</v>
+      </c>
+      <c r="B279" t="s">
+        <v>647</v>
+      </c>
+      <c r="C279" t="s">
         <v>662</v>
       </c>
-      <c r="B279" t="s">
-        <v>647</v>
-      </c>
-      <c r="C279" t="s">
-        <v>383</v>
-      </c>
       <c r="D279" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E279" t="s">
         <v>663</v>
@@ -8063,10 +8063,10 @@
         <v>647</v>
       </c>
       <c r="C280" t="s">
-        <v>513</v>
+        <v>383</v>
       </c>
       <c r="D280" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E280" t="s">
         <v>665</v>
@@ -8083,10 +8083,10 @@
         <v>647</v>
       </c>
       <c r="C281" t="s">
-        <v>231</v>
+        <v>513</v>
       </c>
       <c r="D281" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E281" t="s">
         <v>667</v>
@@ -8103,10 +8103,10 @@
         <v>647</v>
       </c>
       <c r="C282" t="s">
-        <v>660</v>
+        <v>228</v>
       </c>
       <c r="D282" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E282" t="s">
         <v>669</v>
@@ -8123,10 +8123,10 @@
         <v>647</v>
       </c>
       <c r="C283" t="s">
-        <v>231</v>
+        <v>662</v>
       </c>
       <c r="D283" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E283" t="s">
         <v>671</v>
@@ -8143,10 +8143,10 @@
         <v>647</v>
       </c>
       <c r="C284" t="s">
-        <v>513</v>
+        <v>228</v>
       </c>
       <c r="D284" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E284" t="s">
         <v>673</v>
@@ -8166,7 +8166,7 @@
         <v>513</v>
       </c>
       <c r="D285" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E285" t="s">
         <v>675</v>
@@ -8183,10 +8183,10 @@
         <v>647</v>
       </c>
       <c r="C286" t="s">
-        <v>660</v>
+        <v>513</v>
       </c>
       <c r="D286" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E286" t="s">
         <v>677</v>
@@ -8203,13 +8203,13 @@
         <v>647</v>
       </c>
       <c r="C287" t="s">
+        <v>662</v>
+      </c>
+      <c r="D287" t="s">
+        <v>648</v>
+      </c>
+      <c r="E287" t="s">
         <v>679</v>
-      </c>
-      <c r="D287" t="s">
-        <v>649</v>
-      </c>
-      <c r="E287" t="s">
-        <v>680</v>
       </c>
       <c r="F287" s="1">
         <v>46245</v>
@@ -8217,19 +8217,19 @@
     </row>
     <row r="288" spans="1:6">
       <c r="A288" t="s">
+        <v>680</v>
+      </c>
+      <c r="B288" t="s">
+        <v>647</v>
+      </c>
+      <c r="C288" t="s">
         <v>681</v>
       </c>
-      <c r="B288" t="s">
+      <c r="D288" t="s">
+        <v>648</v>
+      </c>
+      <c r="E288" t="s">
         <v>682</v>
-      </c>
-      <c r="C288" t="s">
-        <v>683</v>
-      </c>
-      <c r="D288" t="s">
-        <v>649</v>
-      </c>
-      <c r="E288" t="s">
-        <v>684</v>
       </c>
       <c r="F288" s="1">
         <v>46245</v>
@@ -8237,16 +8237,16 @@
     </row>
     <row r="289" spans="1:6">
       <c r="A289" t="s">
+        <v>683</v>
+      </c>
+      <c r="B289" t="s">
+        <v>684</v>
+      </c>
+      <c r="C289" t="s">
         <v>685</v>
       </c>
-      <c r="B289" t="s">
-        <v>647</v>
-      </c>
-      <c r="C289" t="s">
-        <v>683</v>
-      </c>
       <c r="D289" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E289" t="s">
         <v>686</v>
@@ -8263,10 +8263,10 @@
         <v>647</v>
       </c>
       <c r="C290" t="s">
-        <v>346</v>
+        <v>685</v>
       </c>
       <c r="D290" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E290" t="s">
         <v>688</v>
@@ -8283,10 +8283,10 @@
         <v>647</v>
       </c>
       <c r="C291" t="s">
-        <v>679</v>
+        <v>349</v>
       </c>
       <c r="D291" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E291" t="s">
         <v>690</v>
@@ -8303,10 +8303,10 @@
         <v>647</v>
       </c>
       <c r="C292" t="s">
-        <v>346</v>
+        <v>681</v>
       </c>
       <c r="D292" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E292" t="s">
         <v>692</v>
@@ -8323,10 +8323,10 @@
         <v>647</v>
       </c>
       <c r="C293" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D293" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E293" t="s">
         <v>694</v>
@@ -8343,10 +8343,10 @@
         <v>647</v>
       </c>
       <c r="C294" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D294" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E294" t="s">
         <v>696</v>
@@ -8363,10 +8363,10 @@
         <v>647</v>
       </c>
       <c r="C295" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D295" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E295" t="s">
         <v>698</v>
@@ -8383,10 +8383,10 @@
         <v>647</v>
       </c>
       <c r="C296" t="s">
-        <v>403</v>
+        <v>349</v>
       </c>
       <c r="D296" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E296" t="s">
         <v>700</v>
@@ -8403,10 +8403,10 @@
         <v>647</v>
       </c>
       <c r="C297" t="s">
-        <v>683</v>
+        <v>403</v>
       </c>
       <c r="D297" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E297" t="s">
         <v>702</v>
@@ -8423,13 +8423,13 @@
         <v>647</v>
       </c>
       <c r="C298" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="D298" t="s">
+        <v>648</v>
+      </c>
+      <c r="E298" t="s">
         <v>649</v>
-      </c>
-      <c r="E298" t="s">
-        <v>650</v>
       </c>
       <c r="F298" s="1">
         <v>46245</v>
@@ -8437,16 +8437,16 @@
     </row>
     <row r="299" spans="1:6">
       <c r="A299" t="s">
+        <v>650</v>
+      </c>
+      <c r="B299" t="s">
+        <v>647</v>
+      </c>
+      <c r="C299" t="s">
         <v>651</v>
       </c>
-      <c r="B299" t="s">
-        <v>647</v>
-      </c>
-      <c r="C299" t="s">
-        <v>648</v>
-      </c>
       <c r="D299" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E299" t="s">
         <v>652</v>
@@ -8463,10 +8463,10 @@
         <v>647</v>
       </c>
       <c r="C300" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D300" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E300" t="s">
         <v>654</v>
@@ -8483,10 +8483,10 @@
         <v>647</v>
       </c>
       <c r="C301" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D301" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E301" t="s">
         <v>656</v>
@@ -8503,10 +8503,10 @@
         <v>647</v>
       </c>
       <c r="C302" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D302" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E302" t="s">
         <v>658</v>
@@ -8523,13 +8523,13 @@
         <v>647</v>
       </c>
       <c r="C303" t="s">
+        <v>651</v>
+      </c>
+      <c r="D303" t="s">
+        <v>648</v>
+      </c>
+      <c r="E303" t="s">
         <v>660</v>
-      </c>
-      <c r="D303" t="s">
-        <v>649</v>
-      </c>
-      <c r="E303" t="s">
-        <v>661</v>
       </c>
       <c r="F303" s="1">
         <v>46245</v>
@@ -8537,16 +8537,16 @@
     </row>
     <row r="304" spans="1:6">
       <c r="A304" t="s">
+        <v>661</v>
+      </c>
+      <c r="B304" t="s">
+        <v>647</v>
+      </c>
+      <c r="C304" t="s">
         <v>662</v>
       </c>
-      <c r="B304" t="s">
-        <v>647</v>
-      </c>
-      <c r="C304" t="s">
-        <v>383</v>
-      </c>
       <c r="D304" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E304" t="s">
         <v>663</v>
@@ -8563,10 +8563,10 @@
         <v>647</v>
       </c>
       <c r="C305" t="s">
-        <v>513</v>
+        <v>383</v>
       </c>
       <c r="D305" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E305" t="s">
         <v>665</v>
@@ -8583,10 +8583,10 @@
         <v>647</v>
       </c>
       <c r="C306" t="s">
-        <v>231</v>
+        <v>513</v>
       </c>
       <c r="D306" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E306" t="s">
         <v>667</v>
@@ -8603,10 +8603,10 @@
         <v>647</v>
       </c>
       <c r="C307" t="s">
-        <v>660</v>
+        <v>228</v>
       </c>
       <c r="D307" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E307" t="s">
         <v>669</v>
@@ -8623,10 +8623,10 @@
         <v>647</v>
       </c>
       <c r="C308" t="s">
-        <v>231</v>
+        <v>662</v>
       </c>
       <c r="D308" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E308" t="s">
         <v>671</v>
@@ -8643,10 +8643,10 @@
         <v>647</v>
       </c>
       <c r="C309" t="s">
-        <v>513</v>
+        <v>228</v>
       </c>
       <c r="D309" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E309" t="s">
         <v>673</v>
@@ -8666,7 +8666,7 @@
         <v>513</v>
       </c>
       <c r="D310" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E310" t="s">
         <v>675</v>
@@ -8683,10 +8683,10 @@
         <v>647</v>
       </c>
       <c r="C311" t="s">
-        <v>660</v>
+        <v>513</v>
       </c>
       <c r="D311" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E311" t="s">
         <v>677</v>
@@ -8703,13 +8703,13 @@
         <v>647</v>
       </c>
       <c r="C312" t="s">
+        <v>662</v>
+      </c>
+      <c r="D312" t="s">
+        <v>648</v>
+      </c>
+      <c r="E312" t="s">
         <v>679</v>
-      </c>
-      <c r="D312" t="s">
-        <v>649</v>
-      </c>
-      <c r="E312" t="s">
-        <v>680</v>
       </c>
       <c r="F312" s="1">
         <v>46245</v>
@@ -8717,19 +8717,19 @@
     </row>
     <row r="313" spans="1:6">
       <c r="A313" t="s">
+        <v>680</v>
+      </c>
+      <c r="B313" t="s">
+        <v>647</v>
+      </c>
+      <c r="C313" t="s">
         <v>681</v>
       </c>
-      <c r="B313" t="s">
+      <c r="D313" t="s">
+        <v>648</v>
+      </c>
+      <c r="E313" t="s">
         <v>682</v>
-      </c>
-      <c r="C313" t="s">
-        <v>683</v>
-      </c>
-      <c r="D313" t="s">
-        <v>649</v>
-      </c>
-      <c r="E313" t="s">
-        <v>684</v>
       </c>
       <c r="F313" s="1">
         <v>46245</v>
@@ -8737,16 +8737,16 @@
     </row>
     <row r="314" spans="1:6">
       <c r="A314" t="s">
+        <v>683</v>
+      </c>
+      <c r="B314" t="s">
+        <v>684</v>
+      </c>
+      <c r="C314" t="s">
         <v>685</v>
       </c>
-      <c r="B314" t="s">
-        <v>647</v>
-      </c>
-      <c r="C314" t="s">
-        <v>683</v>
-      </c>
       <c r="D314" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E314" t="s">
         <v>686</v>
@@ -8763,10 +8763,10 @@
         <v>647</v>
       </c>
       <c r="C315" t="s">
-        <v>346</v>
+        <v>685</v>
       </c>
       <c r="D315" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E315" t="s">
         <v>688</v>
@@ -8783,10 +8783,10 @@
         <v>647</v>
       </c>
       <c r="C316" t="s">
-        <v>679</v>
+        <v>349</v>
       </c>
       <c r="D316" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E316" t="s">
         <v>690</v>
@@ -8803,10 +8803,10 @@
         <v>647</v>
       </c>
       <c r="C317" t="s">
-        <v>346</v>
+        <v>681</v>
       </c>
       <c r="D317" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E317" t="s">
         <v>692</v>
@@ -8823,10 +8823,10 @@
         <v>647</v>
       </c>
       <c r="C318" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D318" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E318" t="s">
         <v>694</v>
@@ -8843,10 +8843,10 @@
         <v>647</v>
       </c>
       <c r="C319" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D319" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E319" t="s">
         <v>696</v>
@@ -8863,10 +8863,10 @@
         <v>647</v>
       </c>
       <c r="C320" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D320" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E320" t="s">
         <v>698</v>
@@ -8883,10 +8883,10 @@
         <v>647</v>
       </c>
       <c r="C321" t="s">
-        <v>403</v>
+        <v>349</v>
       </c>
       <c r="D321" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E321" t="s">
         <v>700</v>
@@ -8903,10 +8903,10 @@
         <v>647</v>
       </c>
       <c r="C322" t="s">
-        <v>683</v>
+        <v>403</v>
       </c>
       <c r="D322" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E322" t="s">
         <v>702</v>
@@ -8923,13 +8923,13 @@
         <v>647</v>
       </c>
       <c r="C323" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="D323" t="s">
+        <v>648</v>
+      </c>
+      <c r="E323" t="s">
         <v>649</v>
-      </c>
-      <c r="E323" t="s">
-        <v>650</v>
       </c>
       <c r="F323" s="1">
         <v>46245</v>
@@ -8937,16 +8937,16 @@
     </row>
     <row r="324" spans="1:6">
       <c r="A324" t="s">
+        <v>650</v>
+      </c>
+      <c r="B324" t="s">
+        <v>647</v>
+      </c>
+      <c r="C324" t="s">
         <v>651</v>
       </c>
-      <c r="B324" t="s">
-        <v>647</v>
-      </c>
-      <c r="C324" t="s">
-        <v>648</v>
-      </c>
       <c r="D324" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E324" t="s">
         <v>652</v>
@@ -8963,10 +8963,10 @@
         <v>647</v>
       </c>
       <c r="C325" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D325" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E325" t="s">
         <v>654</v>
@@ -8983,10 +8983,10 @@
         <v>647</v>
       </c>
       <c r="C326" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D326" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E326" t="s">
         <v>656</v>
@@ -9003,10 +9003,10 @@
         <v>647</v>
       </c>
       <c r="C327" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D327" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E327" t="s">
         <v>658</v>
@@ -9023,13 +9023,13 @@
         <v>647</v>
       </c>
       <c r="C328" t="s">
+        <v>651</v>
+      </c>
+      <c r="D328" t="s">
+        <v>648</v>
+      </c>
+      <c r="E328" t="s">
         <v>660</v>
-      </c>
-      <c r="D328" t="s">
-        <v>649</v>
-      </c>
-      <c r="E328" t="s">
-        <v>661</v>
       </c>
       <c r="F328" s="1">
         <v>46245</v>
@@ -9037,16 +9037,16 @@
     </row>
     <row r="329" spans="1:6">
       <c r="A329" t="s">
+        <v>661</v>
+      </c>
+      <c r="B329" t="s">
+        <v>647</v>
+      </c>
+      <c r="C329" t="s">
         <v>662</v>
       </c>
-      <c r="B329" t="s">
-        <v>647</v>
-      </c>
-      <c r="C329" t="s">
-        <v>383</v>
-      </c>
       <c r="D329" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E329" t="s">
         <v>663</v>
@@ -9063,10 +9063,10 @@
         <v>647</v>
       </c>
       <c r="C330" t="s">
-        <v>513</v>
+        <v>383</v>
       </c>
       <c r="D330" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E330" t="s">
         <v>665</v>
@@ -9083,10 +9083,10 @@
         <v>647</v>
       </c>
       <c r="C331" t="s">
-        <v>231</v>
+        <v>513</v>
       </c>
       <c r="D331" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E331" t="s">
         <v>667</v>
@@ -9103,10 +9103,10 @@
         <v>647</v>
       </c>
       <c r="C332" t="s">
-        <v>660</v>
+        <v>228</v>
       </c>
       <c r="D332" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E332" t="s">
         <v>669</v>
@@ -9123,10 +9123,10 @@
         <v>647</v>
       </c>
       <c r="C333" t="s">
-        <v>231</v>
+        <v>662</v>
       </c>
       <c r="D333" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E333" t="s">
         <v>671</v>
@@ -9143,10 +9143,10 @@
         <v>647</v>
       </c>
       <c r="C334" t="s">
-        <v>513</v>
+        <v>228</v>
       </c>
       <c r="D334" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E334" t="s">
         <v>673</v>
@@ -9166,7 +9166,7 @@
         <v>513</v>
       </c>
       <c r="D335" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E335" t="s">
         <v>675</v>
@@ -9183,10 +9183,10 @@
         <v>647</v>
       </c>
       <c r="C336" t="s">
-        <v>660</v>
+        <v>513</v>
       </c>
       <c r="D336" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E336" t="s">
         <v>677</v>
@@ -9203,13 +9203,13 @@
         <v>647</v>
       </c>
       <c r="C337" t="s">
+        <v>662</v>
+      </c>
+      <c r="D337" t="s">
+        <v>648</v>
+      </c>
+      <c r="E337" t="s">
         <v>679</v>
-      </c>
-      <c r="D337" t="s">
-        <v>649</v>
-      </c>
-      <c r="E337" t="s">
-        <v>680</v>
       </c>
       <c r="F337" s="1">
         <v>46245</v>
@@ -9217,19 +9217,19 @@
     </row>
     <row r="338" spans="1:6">
       <c r="A338" t="s">
+        <v>680</v>
+      </c>
+      <c r="B338" t="s">
+        <v>647</v>
+      </c>
+      <c r="C338" t="s">
         <v>681</v>
       </c>
-      <c r="B338" t="s">
+      <c r="D338" t="s">
+        <v>648</v>
+      </c>
+      <c r="E338" t="s">
         <v>682</v>
-      </c>
-      <c r="C338" t="s">
-        <v>683</v>
-      </c>
-      <c r="D338" t="s">
-        <v>649</v>
-      </c>
-      <c r="E338" t="s">
-        <v>684</v>
       </c>
       <c r="F338" s="1">
         <v>46245</v>
@@ -9237,16 +9237,16 @@
     </row>
     <row r="339" spans="1:6">
       <c r="A339" t="s">
+        <v>683</v>
+      </c>
+      <c r="B339" t="s">
+        <v>684</v>
+      </c>
+      <c r="C339" t="s">
         <v>685</v>
       </c>
-      <c r="B339" t="s">
-        <v>647</v>
-      </c>
-      <c r="C339" t="s">
-        <v>683</v>
-      </c>
       <c r="D339" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E339" t="s">
         <v>686</v>
@@ -9263,10 +9263,10 @@
         <v>647</v>
       </c>
       <c r="C340" t="s">
-        <v>346</v>
+        <v>685</v>
       </c>
       <c r="D340" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E340" t="s">
         <v>688</v>
@@ -9283,10 +9283,10 @@
         <v>647</v>
       </c>
       <c r="C341" t="s">
-        <v>679</v>
+        <v>349</v>
       </c>
       <c r="D341" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E341" t="s">
         <v>690</v>
@@ -9303,10 +9303,10 @@
         <v>647</v>
       </c>
       <c r="C342" t="s">
-        <v>346</v>
+        <v>681</v>
       </c>
       <c r="D342" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E342" t="s">
         <v>692</v>
@@ -9323,10 +9323,10 @@
         <v>647</v>
       </c>
       <c r="C343" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D343" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E343" t="s">
         <v>694</v>
@@ -9343,10 +9343,10 @@
         <v>647</v>
       </c>
       <c r="C344" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D344" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E344" t="s">
         <v>696</v>
@@ -9363,10 +9363,10 @@
         <v>647</v>
       </c>
       <c r="C345" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D345" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E345" t="s">
         <v>698</v>
@@ -9383,10 +9383,10 @@
         <v>647</v>
       </c>
       <c r="C346" t="s">
-        <v>403</v>
+        <v>349</v>
       </c>
       <c r="D346" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E346" t="s">
         <v>700</v>
@@ -9403,10 +9403,10 @@
         <v>647</v>
       </c>
       <c r="C347" t="s">
-        <v>683</v>
+        <v>403</v>
       </c>
       <c r="D347" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E347" t="s">
         <v>702</v>
@@ -9423,13 +9423,13 @@
         <v>647</v>
       </c>
       <c r="C348" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="D348" t="s">
+        <v>648</v>
+      </c>
+      <c r="E348" t="s">
         <v>649</v>
-      </c>
-      <c r="E348" t="s">
-        <v>650</v>
       </c>
       <c r="F348" s="1">
         <v>46245</v>
@@ -9437,16 +9437,16 @@
     </row>
     <row r="349" spans="1:6">
       <c r="A349" t="s">
+        <v>650</v>
+      </c>
+      <c r="B349" t="s">
+        <v>647</v>
+      </c>
+      <c r="C349" t="s">
         <v>651</v>
       </c>
-      <c r="B349" t="s">
-        <v>647</v>
-      </c>
-      <c r="C349" t="s">
-        <v>648</v>
-      </c>
       <c r="D349" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E349" t="s">
         <v>652</v>
@@ -9463,10 +9463,10 @@
         <v>647</v>
       </c>
       <c r="C350" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D350" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E350" t="s">
         <v>654</v>
@@ -9483,10 +9483,10 @@
         <v>647</v>
       </c>
       <c r="C351" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D351" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E351" t="s">
         <v>656</v>
@@ -9503,10 +9503,10 @@
         <v>647</v>
       </c>
       <c r="C352" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D352" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E352" t="s">
         <v>658</v>
@@ -9523,13 +9523,13 @@
         <v>647</v>
       </c>
       <c r="C353" t="s">
+        <v>651</v>
+      </c>
+      <c r="D353" t="s">
+        <v>648</v>
+      </c>
+      <c r="E353" t="s">
         <v>660</v>
-      </c>
-      <c r="D353" t="s">
-        <v>649</v>
-      </c>
-      <c r="E353" t="s">
-        <v>661</v>
       </c>
       <c r="F353" s="1">
         <v>46245</v>
@@ -9537,16 +9537,16 @@
     </row>
     <row r="354" spans="1:6">
       <c r="A354" t="s">
+        <v>661</v>
+      </c>
+      <c r="B354" t="s">
+        <v>647</v>
+      </c>
+      <c r="C354" t="s">
         <v>662</v>
       </c>
-      <c r="B354" t="s">
-        <v>647</v>
-      </c>
-      <c r="C354" t="s">
-        <v>383</v>
-      </c>
       <c r="D354" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E354" t="s">
         <v>663</v>
@@ -9563,10 +9563,10 @@
         <v>647</v>
       </c>
       <c r="C355" t="s">
-        <v>513</v>
+        <v>383</v>
       </c>
       <c r="D355" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E355" t="s">
         <v>665</v>
@@ -9583,10 +9583,10 @@
         <v>647</v>
       </c>
       <c r="C356" t="s">
-        <v>231</v>
+        <v>513</v>
       </c>
       <c r="D356" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E356" t="s">
         <v>667</v>
@@ -9603,10 +9603,10 @@
         <v>647</v>
       </c>
       <c r="C357" t="s">
-        <v>660</v>
+        <v>228</v>
       </c>
       <c r="D357" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E357" t="s">
         <v>669</v>
@@ -9623,10 +9623,10 @@
         <v>647</v>
       </c>
       <c r="C358" t="s">
-        <v>231</v>
+        <v>662</v>
       </c>
       <c r="D358" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E358" t="s">
         <v>671</v>
@@ -9643,10 +9643,10 @@
         <v>647</v>
       </c>
       <c r="C359" t="s">
-        <v>513</v>
+        <v>228</v>
       </c>
       <c r="D359" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E359" t="s">
         <v>673</v>
@@ -9666,7 +9666,7 @@
         <v>513</v>
       </c>
       <c r="D360" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E360" t="s">
         <v>675</v>
@@ -9683,10 +9683,10 @@
         <v>647</v>
       </c>
       <c r="C361" t="s">
-        <v>660</v>
+        <v>513</v>
       </c>
       <c r="D361" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E361" t="s">
         <v>677</v>
@@ -9703,13 +9703,13 @@
         <v>647</v>
       </c>
       <c r="C362" t="s">
+        <v>662</v>
+      </c>
+      <c r="D362" t="s">
+        <v>648</v>
+      </c>
+      <c r="E362" t="s">
         <v>679</v>
-      </c>
-      <c r="D362" t="s">
-        <v>649</v>
-      </c>
-      <c r="E362" t="s">
-        <v>680</v>
       </c>
       <c r="F362" s="1">
         <v>46245</v>
@@ -9717,19 +9717,19 @@
     </row>
     <row r="363" spans="1:6">
       <c r="A363" t="s">
+        <v>680</v>
+      </c>
+      <c r="B363" t="s">
+        <v>647</v>
+      </c>
+      <c r="C363" t="s">
         <v>681</v>
       </c>
-      <c r="B363" t="s">
+      <c r="D363" t="s">
+        <v>648</v>
+      </c>
+      <c r="E363" t="s">
         <v>682</v>
-      </c>
-      <c r="C363" t="s">
-        <v>683</v>
-      </c>
-      <c r="D363" t="s">
-        <v>649</v>
-      </c>
-      <c r="E363" t="s">
-        <v>684</v>
       </c>
       <c r="F363" s="1">
         <v>46245</v>
@@ -9737,16 +9737,16 @@
     </row>
     <row r="364" spans="1:6">
       <c r="A364" t="s">
+        <v>683</v>
+      </c>
+      <c r="B364" t="s">
+        <v>684</v>
+      </c>
+      <c r="C364" t="s">
         <v>685</v>
       </c>
-      <c r="B364" t="s">
-        <v>647</v>
-      </c>
-      <c r="C364" t="s">
-        <v>683</v>
-      </c>
       <c r="D364" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E364" t="s">
         <v>686</v>
@@ -9763,10 +9763,10 @@
         <v>647</v>
       </c>
       <c r="C365" t="s">
-        <v>346</v>
+        <v>685</v>
       </c>
       <c r="D365" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E365" t="s">
         <v>688</v>
@@ -9783,10 +9783,10 @@
         <v>647</v>
       </c>
       <c r="C366" t="s">
-        <v>679</v>
+        <v>349</v>
       </c>
       <c r="D366" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E366" t="s">
         <v>690</v>
@@ -9803,10 +9803,10 @@
         <v>647</v>
       </c>
       <c r="C367" t="s">
-        <v>346</v>
+        <v>681</v>
       </c>
       <c r="D367" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E367" t="s">
         <v>692</v>
@@ -9823,10 +9823,10 @@
         <v>647</v>
       </c>
       <c r="C368" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D368" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E368" t="s">
         <v>694</v>
@@ -9843,10 +9843,10 @@
         <v>647</v>
       </c>
       <c r="C369" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D369" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E369" t="s">
         <v>696</v>
@@ -9863,10 +9863,10 @@
         <v>647</v>
       </c>
       <c r="C370" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D370" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E370" t="s">
         <v>698</v>
@@ -9883,10 +9883,10 @@
         <v>647</v>
       </c>
       <c r="C371" t="s">
-        <v>403</v>
+        <v>349</v>
       </c>
       <c r="D371" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E371" t="s">
         <v>700</v>
@@ -9903,10 +9903,10 @@
         <v>647</v>
       </c>
       <c r="C372" t="s">
-        <v>683</v>
+        <v>403</v>
       </c>
       <c r="D372" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E372" t="s">
         <v>702</v>
@@ -9923,13 +9923,13 @@
         <v>647</v>
       </c>
       <c r="C373" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="D373" t="s">
+        <v>648</v>
+      </c>
+      <c r="E373" t="s">
         <v>649</v>
-      </c>
-      <c r="E373" t="s">
-        <v>650</v>
       </c>
       <c r="F373" s="1">
         <v>46245</v>
@@ -9937,16 +9937,16 @@
     </row>
     <row r="374" spans="1:6">
       <c r="A374" t="s">
+        <v>650</v>
+      </c>
+      <c r="B374" t="s">
+        <v>647</v>
+      </c>
+      <c r="C374" t="s">
         <v>651</v>
       </c>
-      <c r="B374" t="s">
-        <v>647</v>
-      </c>
-      <c r="C374" t="s">
-        <v>648</v>
-      </c>
       <c r="D374" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E374" t="s">
         <v>652</v>
@@ -9963,10 +9963,10 @@
         <v>647</v>
       </c>
       <c r="C375" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D375" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E375" t="s">
         <v>654</v>
@@ -9983,10 +9983,10 @@
         <v>647</v>
       </c>
       <c r="C376" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D376" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E376" t="s">
         <v>656</v>
@@ -10003,10 +10003,10 @@
         <v>647</v>
       </c>
       <c r="C377" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D377" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E377" t="s">
         <v>658</v>
@@ -10023,13 +10023,13 @@
         <v>647</v>
       </c>
       <c r="C378" t="s">
+        <v>651</v>
+      </c>
+      <c r="D378" t="s">
+        <v>648</v>
+      </c>
+      <c r="E378" t="s">
         <v>660</v>
-      </c>
-      <c r="D378" t="s">
-        <v>649</v>
-      </c>
-      <c r="E378" t="s">
-        <v>661</v>
       </c>
       <c r="F378" s="1">
         <v>46245</v>
@@ -10037,16 +10037,16 @@
     </row>
     <row r="379" spans="1:6">
       <c r="A379" t="s">
+        <v>661</v>
+      </c>
+      <c r="B379" t="s">
+        <v>647</v>
+      </c>
+      <c r="C379" t="s">
         <v>662</v>
       </c>
-      <c r="B379" t="s">
-        <v>647</v>
-      </c>
-      <c r="C379" t="s">
-        <v>383</v>
-      </c>
       <c r="D379" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E379" t="s">
         <v>663</v>
@@ -10063,10 +10063,10 @@
         <v>647</v>
       </c>
       <c r="C380" t="s">
-        <v>513</v>
+        <v>383</v>
       </c>
       <c r="D380" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E380" t="s">
         <v>665</v>
@@ -10083,10 +10083,10 @@
         <v>647</v>
       </c>
       <c r="C381" t="s">
-        <v>231</v>
+        <v>513</v>
       </c>
       <c r="D381" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E381" t="s">
         <v>667</v>
@@ -10103,10 +10103,10 @@
         <v>647</v>
       </c>
       <c r="C382" t="s">
-        <v>660</v>
+        <v>228</v>
       </c>
       <c r="D382" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E382" t="s">
         <v>669</v>
@@ -10123,10 +10123,10 @@
         <v>647</v>
       </c>
       <c r="C383" t="s">
-        <v>231</v>
+        <v>662</v>
       </c>
       <c r="D383" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E383" t="s">
         <v>671</v>
@@ -10143,10 +10143,10 @@
         <v>647</v>
       </c>
       <c r="C384" t="s">
-        <v>513</v>
+        <v>228</v>
       </c>
       <c r="D384" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E384" t="s">
         <v>673</v>
@@ -10166,7 +10166,7 @@
         <v>513</v>
       </c>
       <c r="D385" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E385" t="s">
         <v>675</v>
@@ -10183,10 +10183,10 @@
         <v>647</v>
       </c>
       <c r="C386" t="s">
-        <v>660</v>
+        <v>513</v>
       </c>
       <c r="D386" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E386" t="s">
         <v>677</v>
@@ -10203,13 +10203,13 @@
         <v>647</v>
       </c>
       <c r="C387" t="s">
+        <v>662</v>
+      </c>
+      <c r="D387" t="s">
+        <v>648</v>
+      </c>
+      <c r="E387" t="s">
         <v>679</v>
-      </c>
-      <c r="D387" t="s">
-        <v>649</v>
-      </c>
-      <c r="E387" t="s">
-        <v>680</v>
       </c>
       <c r="F387" s="1">
         <v>46245</v>
@@ -10217,19 +10217,19 @@
     </row>
     <row r="388" spans="1:6">
       <c r="A388" t="s">
+        <v>680</v>
+      </c>
+      <c r="B388" t="s">
+        <v>647</v>
+      </c>
+      <c r="C388" t="s">
         <v>681</v>
       </c>
-      <c r="B388" t="s">
+      <c r="D388" t="s">
+        <v>648</v>
+      </c>
+      <c r="E388" t="s">
         <v>682</v>
-      </c>
-      <c r="C388" t="s">
-        <v>683</v>
-      </c>
-      <c r="D388" t="s">
-        <v>649</v>
-      </c>
-      <c r="E388" t="s">
-        <v>684</v>
       </c>
       <c r="F388" s="1">
         <v>46245</v>
@@ -10237,16 +10237,16 @@
     </row>
     <row r="389" spans="1:6">
       <c r="A389" t="s">
+        <v>683</v>
+      </c>
+      <c r="B389" t="s">
+        <v>684</v>
+      </c>
+      <c r="C389" t="s">
         <v>685</v>
       </c>
-      <c r="B389" t="s">
-        <v>647</v>
-      </c>
-      <c r="C389" t="s">
-        <v>683</v>
-      </c>
       <c r="D389" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E389" t="s">
         <v>686</v>
@@ -10263,10 +10263,10 @@
         <v>647</v>
       </c>
       <c r="C390" t="s">
-        <v>346</v>
+        <v>685</v>
       </c>
       <c r="D390" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E390" t="s">
         <v>688</v>
@@ -10283,10 +10283,10 @@
         <v>647</v>
       </c>
       <c r="C391" t="s">
-        <v>679</v>
+        <v>349</v>
       </c>
       <c r="D391" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E391" t="s">
         <v>690</v>
@@ -10303,10 +10303,10 @@
         <v>647</v>
       </c>
       <c r="C392" t="s">
-        <v>346</v>
+        <v>681</v>
       </c>
       <c r="D392" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E392" t="s">
         <v>692</v>
@@ -10323,10 +10323,10 @@
         <v>647</v>
       </c>
       <c r="C393" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D393" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E393" t="s">
         <v>694</v>
@@ -10343,10 +10343,10 @@
         <v>647</v>
       </c>
       <c r="C394" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D394" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E394" t="s">
         <v>696</v>
@@ -10363,10 +10363,10 @@
         <v>647</v>
       </c>
       <c r="C395" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D395" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E395" t="s">
         <v>698</v>
@@ -10383,10 +10383,10 @@
         <v>647</v>
       </c>
       <c r="C396" t="s">
-        <v>403</v>
+        <v>349</v>
       </c>
       <c r="D396" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E396" t="s">
         <v>700</v>
@@ -10403,10 +10403,10 @@
         <v>647</v>
       </c>
       <c r="C397" t="s">
-        <v>683</v>
+        <v>403</v>
       </c>
       <c r="D397" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E397" t="s">
         <v>702</v>
@@ -10423,13 +10423,13 @@
         <v>647</v>
       </c>
       <c r="C398" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="D398" t="s">
+        <v>648</v>
+      </c>
+      <c r="E398" t="s">
         <v>649</v>
-      </c>
-      <c r="E398" t="s">
-        <v>650</v>
       </c>
       <c r="F398" s="1">
         <v>46245</v>
@@ -10437,16 +10437,16 @@
     </row>
     <row r="399" spans="1:6">
       <c r="A399" t="s">
+        <v>650</v>
+      </c>
+      <c r="B399" t="s">
+        <v>647</v>
+      </c>
+      <c r="C399" t="s">
         <v>651</v>
       </c>
-      <c r="B399" t="s">
-        <v>647</v>
-      </c>
-      <c r="C399" t="s">
-        <v>648</v>
-      </c>
       <c r="D399" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E399" t="s">
         <v>652</v>
@@ -10463,10 +10463,10 @@
         <v>647</v>
       </c>
       <c r="C400" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D400" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E400" t="s">
         <v>654</v>
@@ -10483,10 +10483,10 @@
         <v>647</v>
       </c>
       <c r="C401" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D401" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E401" t="s">
         <v>656</v>
@@ -10503,10 +10503,10 @@
         <v>647</v>
       </c>
       <c r="C402" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D402" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E402" t="s">
         <v>658</v>
@@ -10523,13 +10523,13 @@
         <v>647</v>
       </c>
       <c r="C403" t="s">
+        <v>651</v>
+      </c>
+      <c r="D403" t="s">
+        <v>648</v>
+      </c>
+      <c r="E403" t="s">
         <v>660</v>
-      </c>
-      <c r="D403" t="s">
-        <v>649</v>
-      </c>
-      <c r="E403" t="s">
-        <v>661</v>
       </c>
       <c r="F403" s="1">
         <v>46245</v>
@@ -10537,16 +10537,16 @@
     </row>
     <row r="404" spans="1:6">
       <c r="A404" t="s">
+        <v>661</v>
+      </c>
+      <c r="B404" t="s">
+        <v>647</v>
+      </c>
+      <c r="C404" t="s">
         <v>662</v>
       </c>
-      <c r="B404" t="s">
-        <v>647</v>
-      </c>
-      <c r="C404" t="s">
-        <v>383</v>
-      </c>
       <c r="D404" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E404" t="s">
         <v>663</v>
@@ -10563,10 +10563,10 @@
         <v>647</v>
       </c>
       <c r="C405" t="s">
-        <v>513</v>
+        <v>383</v>
       </c>
       <c r="D405" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E405" t="s">
         <v>665</v>
@@ -10583,10 +10583,10 @@
         <v>647</v>
       </c>
       <c r="C406" t="s">
-        <v>231</v>
+        <v>513</v>
       </c>
       <c r="D406" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E406" t="s">
         <v>667</v>
@@ -10603,10 +10603,10 @@
         <v>647</v>
       </c>
       <c r="C407" t="s">
-        <v>660</v>
+        <v>228</v>
       </c>
       <c r="D407" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E407" t="s">
         <v>669</v>
@@ -10623,10 +10623,10 @@
         <v>647</v>
       </c>
       <c r="C408" t="s">
-        <v>231</v>
+        <v>662</v>
       </c>
       <c r="D408" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E408" t="s">
         <v>671</v>
@@ -10643,10 +10643,10 @@
         <v>647</v>
       </c>
       <c r="C409" t="s">
-        <v>513</v>
+        <v>228</v>
       </c>
       <c r="D409" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E409" t="s">
         <v>673</v>
@@ -10666,7 +10666,7 @@
         <v>513</v>
       </c>
       <c r="D410" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E410" t="s">
         <v>675</v>
@@ -10683,10 +10683,10 @@
         <v>647</v>
       </c>
       <c r="C411" t="s">
-        <v>660</v>
+        <v>513</v>
       </c>
       <c r="D411" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E411" t="s">
         <v>677</v>
@@ -10703,13 +10703,13 @@
         <v>647</v>
       </c>
       <c r="C412" t="s">
+        <v>662</v>
+      </c>
+      <c r="D412" t="s">
+        <v>648</v>
+      </c>
+      <c r="E412" t="s">
         <v>679</v>
-      </c>
-      <c r="D412" t="s">
-        <v>649</v>
-      </c>
-      <c r="E412" t="s">
-        <v>680</v>
       </c>
       <c r="F412" s="1">
         <v>46245</v>
@@ -10717,19 +10717,19 @@
     </row>
     <row r="413" spans="1:6">
       <c r="A413" t="s">
+        <v>680</v>
+      </c>
+      <c r="B413" t="s">
+        <v>647</v>
+      </c>
+      <c r="C413" t="s">
         <v>681</v>
       </c>
-      <c r="B413" t="s">
+      <c r="D413" t="s">
+        <v>648</v>
+      </c>
+      <c r="E413" t="s">
         <v>682</v>
-      </c>
-      <c r="C413" t="s">
-        <v>683</v>
-      </c>
-      <c r="D413" t="s">
-        <v>649</v>
-      </c>
-      <c r="E413" t="s">
-        <v>684</v>
       </c>
       <c r="F413" s="1">
         <v>46245</v>
@@ -10737,16 +10737,16 @@
     </row>
     <row r="414" spans="1:6">
       <c r="A414" t="s">
+        <v>683</v>
+      </c>
+      <c r="B414" t="s">
+        <v>684</v>
+      </c>
+      <c r="C414" t="s">
         <v>685</v>
       </c>
-      <c r="B414" t="s">
-        <v>647</v>
-      </c>
-      <c r="C414" t="s">
-        <v>683</v>
-      </c>
       <c r="D414" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E414" t="s">
         <v>686</v>
@@ -10763,10 +10763,10 @@
         <v>647</v>
       </c>
       <c r="C415" t="s">
-        <v>346</v>
+        <v>685</v>
       </c>
       <c r="D415" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E415" t="s">
         <v>688</v>
@@ -10783,10 +10783,10 @@
         <v>647</v>
       </c>
       <c r="C416" t="s">
-        <v>679</v>
+        <v>349</v>
       </c>
       <c r="D416" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E416" t="s">
         <v>690</v>
@@ -10803,10 +10803,10 @@
         <v>647</v>
       </c>
       <c r="C417" t="s">
-        <v>346</v>
+        <v>681</v>
       </c>
       <c r="D417" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E417" t="s">
         <v>692</v>
@@ -10823,10 +10823,10 @@
         <v>647</v>
       </c>
       <c r="C418" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D418" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E418" t="s">
         <v>694</v>
@@ -10843,10 +10843,10 @@
         <v>647</v>
       </c>
       <c r="C419" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D419" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E419" t="s">
         <v>696</v>
@@ -10863,10 +10863,10 @@
         <v>647</v>
       </c>
       <c r="C420" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D420" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E420" t="s">
         <v>698</v>
@@ -10883,10 +10883,10 @@
         <v>647</v>
       </c>
       <c r="C421" t="s">
-        <v>403</v>
+        <v>349</v>
       </c>
       <c r="D421" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E421" t="s">
         <v>700</v>
@@ -10903,10 +10903,10 @@
         <v>647</v>
       </c>
       <c r="C422" t="s">
-        <v>683</v>
+        <v>403</v>
       </c>
       <c r="D422" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E422" t="s">
         <v>702</v>
@@ -10923,13 +10923,13 @@
         <v>647</v>
       </c>
       <c r="C423" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="D423" t="s">
+        <v>648</v>
+      </c>
+      <c r="E423" t="s">
         <v>649</v>
-      </c>
-      <c r="E423" t="s">
-        <v>650</v>
       </c>
       <c r="F423" s="1">
         <v>46245</v>
@@ -10937,16 +10937,16 @@
     </row>
     <row r="424" spans="1:6">
       <c r="A424" t="s">
+        <v>650</v>
+      </c>
+      <c r="B424" t="s">
+        <v>647</v>
+      </c>
+      <c r="C424" t="s">
         <v>651</v>
       </c>
-      <c r="B424" t="s">
-        <v>647</v>
-      </c>
-      <c r="C424" t="s">
-        <v>648</v>
-      </c>
       <c r="D424" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E424" t="s">
         <v>652</v>
@@ -10963,10 +10963,10 @@
         <v>647</v>
       </c>
       <c r="C425" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D425" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E425" t="s">
         <v>654</v>
@@ -10983,10 +10983,10 @@
         <v>647</v>
       </c>
       <c r="C426" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D426" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E426" t="s">
         <v>656</v>
@@ -11003,10 +11003,10 @@
         <v>647</v>
       </c>
       <c r="C427" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D427" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E427" t="s">
         <v>658</v>
@@ -11023,13 +11023,13 @@
         <v>647</v>
       </c>
       <c r="C428" t="s">
+        <v>651</v>
+      </c>
+      <c r="D428" t="s">
+        <v>648</v>
+      </c>
+      <c r="E428" t="s">
         <v>660</v>
-      </c>
-      <c r="D428" t="s">
-        <v>649</v>
-      </c>
-      <c r="E428" t="s">
-        <v>661</v>
       </c>
       <c r="F428" s="1">
         <v>46245</v>
@@ -11037,16 +11037,16 @@
     </row>
     <row r="429" spans="1:6">
       <c r="A429" t="s">
+        <v>661</v>
+      </c>
+      <c r="B429" t="s">
+        <v>647</v>
+      </c>
+      <c r="C429" t="s">
         <v>662</v>
       </c>
-      <c r="B429" t="s">
-        <v>647</v>
-      </c>
-      <c r="C429" t="s">
-        <v>383</v>
-      </c>
       <c r="D429" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E429" t="s">
         <v>663</v>
@@ -11063,10 +11063,10 @@
         <v>647</v>
       </c>
       <c r="C430" t="s">
-        <v>513</v>
+        <v>383</v>
       </c>
       <c r="D430" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E430" t="s">
         <v>665</v>
@@ -11083,10 +11083,10 @@
         <v>647</v>
       </c>
       <c r="C431" t="s">
-        <v>231</v>
+        <v>513</v>
       </c>
       <c r="D431" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E431" t="s">
         <v>667</v>
@@ -11103,10 +11103,10 @@
         <v>647</v>
       </c>
       <c r="C432" t="s">
-        <v>660</v>
+        <v>228</v>
       </c>
       <c r="D432" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E432" t="s">
         <v>669</v>
@@ -11123,10 +11123,10 @@
         <v>647</v>
       </c>
       <c r="C433" t="s">
-        <v>231</v>
+        <v>662</v>
       </c>
       <c r="D433" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E433" t="s">
         <v>671</v>
@@ -11143,10 +11143,10 @@
         <v>647</v>
       </c>
       <c r="C434" t="s">
-        <v>513</v>
+        <v>228</v>
       </c>
       <c r="D434" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E434" t="s">
         <v>673</v>
@@ -11166,7 +11166,7 @@
         <v>513</v>
       </c>
       <c r="D435" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E435" t="s">
         <v>675</v>
@@ -11183,10 +11183,10 @@
         <v>647</v>
       </c>
       <c r="C436" t="s">
-        <v>660</v>
+        <v>513</v>
       </c>
       <c r="D436" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E436" t="s">
         <v>677</v>
@@ -11203,13 +11203,13 @@
         <v>647</v>
       </c>
       <c r="C437" t="s">
+        <v>662</v>
+      </c>
+      <c r="D437" t="s">
+        <v>648</v>
+      </c>
+      <c r="E437" t="s">
         <v>679</v>
-      </c>
-      <c r="D437" t="s">
-        <v>649</v>
-      </c>
-      <c r="E437" t="s">
-        <v>680</v>
       </c>
       <c r="F437" s="1">
         <v>46245</v>
@@ -11217,19 +11217,19 @@
     </row>
     <row r="438" spans="1:6">
       <c r="A438" t="s">
+        <v>680</v>
+      </c>
+      <c r="B438" t="s">
+        <v>647</v>
+      </c>
+      <c r="C438" t="s">
         <v>681</v>
       </c>
-      <c r="B438" t="s">
+      <c r="D438" t="s">
+        <v>648</v>
+      </c>
+      <c r="E438" t="s">
         <v>682</v>
-      </c>
-      <c r="C438" t="s">
-        <v>683</v>
-      </c>
-      <c r="D438" t="s">
-        <v>649</v>
-      </c>
-      <c r="E438" t="s">
-        <v>684</v>
       </c>
       <c r="F438" s="1">
         <v>46245</v>
@@ -11237,16 +11237,16 @@
     </row>
     <row r="439" spans="1:6">
       <c r="A439" t="s">
+        <v>683</v>
+      </c>
+      <c r="B439" t="s">
+        <v>684</v>
+      </c>
+      <c r="C439" t="s">
         <v>685</v>
       </c>
-      <c r="B439" t="s">
-        <v>647</v>
-      </c>
-      <c r="C439" t="s">
-        <v>683</v>
-      </c>
       <c r="D439" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E439" t="s">
         <v>686</v>
@@ -11263,10 +11263,10 @@
         <v>647</v>
       </c>
       <c r="C440" t="s">
-        <v>346</v>
+        <v>685</v>
       </c>
       <c r="D440" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E440" t="s">
         <v>688</v>
@@ -11283,10 +11283,10 @@
         <v>647</v>
       </c>
       <c r="C441" t="s">
-        <v>679</v>
+        <v>349</v>
       </c>
       <c r="D441" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E441" t="s">
         <v>690</v>
@@ -11303,10 +11303,10 @@
         <v>647</v>
       </c>
       <c r="C442" t="s">
-        <v>346</v>
+        <v>681</v>
       </c>
       <c r="D442" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E442" t="s">
         <v>692</v>
@@ -11323,10 +11323,10 @@
         <v>647</v>
       </c>
       <c r="C443" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D443" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E443" t="s">
         <v>694</v>
@@ -11343,10 +11343,10 @@
         <v>647</v>
       </c>
       <c r="C444" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D444" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E444" t="s">
         <v>696</v>
@@ -11363,10 +11363,10 @@
         <v>647</v>
       </c>
       <c r="C445" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D445" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E445" t="s">
         <v>698</v>
@@ -11383,10 +11383,10 @@
         <v>647</v>
       </c>
       <c r="C446" t="s">
-        <v>403</v>
+        <v>349</v>
       </c>
       <c r="D446" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E446" t="s">
         <v>700</v>
@@ -11403,10 +11403,10 @@
         <v>647</v>
       </c>
       <c r="C447" t="s">
-        <v>683</v>
+        <v>403</v>
       </c>
       <c r="D447" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E447" t="s">
         <v>702</v>
@@ -11423,13 +11423,13 @@
         <v>647</v>
       </c>
       <c r="C448" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="D448" t="s">
+        <v>648</v>
+      </c>
+      <c r="E448" t="s">
         <v>649</v>
-      </c>
-      <c r="E448" t="s">
-        <v>650</v>
       </c>
       <c r="F448" s="1">
         <v>46245</v>
@@ -11437,16 +11437,16 @@
     </row>
     <row r="449" spans="1:6">
       <c r="A449" t="s">
+        <v>650</v>
+      </c>
+      <c r="B449" t="s">
+        <v>647</v>
+      </c>
+      <c r="C449" t="s">
         <v>651</v>
       </c>
-      <c r="B449" t="s">
-        <v>647</v>
-      </c>
-      <c r="C449" t="s">
-        <v>648</v>
-      </c>
       <c r="D449" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E449" t="s">
         <v>652</v>
@@ -11463,10 +11463,10 @@
         <v>647</v>
       </c>
       <c r="C450" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D450" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E450" t="s">
         <v>654</v>
@@ -11483,10 +11483,10 @@
         <v>647</v>
       </c>
       <c r="C451" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D451" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E451" t="s">
         <v>656</v>
@@ -11503,10 +11503,10 @@
         <v>647</v>
       </c>
       <c r="C452" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D452" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E452" t="s">
         <v>658</v>
@@ -11523,13 +11523,13 @@
         <v>647</v>
       </c>
       <c r="C453" t="s">
+        <v>651</v>
+      </c>
+      <c r="D453" t="s">
+        <v>648</v>
+      </c>
+      <c r="E453" t="s">
         <v>660</v>
-      </c>
-      <c r="D453" t="s">
-        <v>649</v>
-      </c>
-      <c r="E453" t="s">
-        <v>661</v>
       </c>
       <c r="F453" s="1">
         <v>46245</v>
@@ -11537,16 +11537,16 @@
     </row>
     <row r="454" spans="1:6">
       <c r="A454" t="s">
+        <v>661</v>
+      </c>
+      <c r="B454" t="s">
+        <v>647</v>
+      </c>
+      <c r="C454" t="s">
         <v>662</v>
       </c>
-      <c r="B454" t="s">
-        <v>647</v>
-      </c>
-      <c r="C454" t="s">
-        <v>383</v>
-      </c>
       <c r="D454" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E454" t="s">
         <v>663</v>
@@ -11563,10 +11563,10 @@
         <v>647</v>
       </c>
       <c r="C455" t="s">
-        <v>513</v>
+        <v>383</v>
       </c>
       <c r="D455" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E455" t="s">
         <v>665</v>
@@ -11583,10 +11583,10 @@
         <v>647</v>
       </c>
       <c r="C456" t="s">
-        <v>231</v>
+        <v>513</v>
       </c>
       <c r="D456" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E456" t="s">
         <v>667</v>
@@ -11603,10 +11603,10 @@
         <v>647</v>
       </c>
       <c r="C457" t="s">
-        <v>660</v>
+        <v>228</v>
       </c>
       <c r="D457" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E457" t="s">
         <v>669</v>
@@ -11623,10 +11623,10 @@
         <v>647</v>
       </c>
       <c r="C458" t="s">
-        <v>231</v>
+        <v>662</v>
       </c>
       <c r="D458" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E458" t="s">
         <v>671</v>
@@ -11643,10 +11643,10 @@
         <v>647</v>
       </c>
       <c r="C459" t="s">
-        <v>513</v>
+        <v>228</v>
       </c>
       <c r="D459" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E459" t="s">
         <v>673</v>
@@ -11666,7 +11666,7 @@
         <v>513</v>
       </c>
       <c r="D460" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E460" t="s">
         <v>675</v>
@@ -11683,10 +11683,10 @@
         <v>647</v>
       </c>
       <c r="C461" t="s">
-        <v>660</v>
+        <v>513</v>
       </c>
       <c r="D461" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E461" t="s">
         <v>677</v>
@@ -11703,13 +11703,13 @@
         <v>647</v>
       </c>
       <c r="C462" t="s">
+        <v>662</v>
+      </c>
+      <c r="D462" t="s">
+        <v>648</v>
+      </c>
+      <c r="E462" t="s">
         <v>679</v>
-      </c>
-      <c r="D462" t="s">
-        <v>649</v>
-      </c>
-      <c r="E462" t="s">
-        <v>680</v>
       </c>
       <c r="F462" s="1">
         <v>46245</v>
@@ -11717,19 +11717,19 @@
     </row>
     <row r="463" spans="1:6">
       <c r="A463" t="s">
+        <v>680</v>
+      </c>
+      <c r="B463" t="s">
+        <v>647</v>
+      </c>
+      <c r="C463" t="s">
         <v>681</v>
       </c>
-      <c r="B463" t="s">
+      <c r="D463" t="s">
+        <v>648</v>
+      </c>
+      <c r="E463" t="s">
         <v>682</v>
-      </c>
-      <c r="C463" t="s">
-        <v>683</v>
-      </c>
-      <c r="D463" t="s">
-        <v>649</v>
-      </c>
-      <c r="E463" t="s">
-        <v>684</v>
       </c>
       <c r="F463" s="1">
         <v>46245</v>
@@ -11737,16 +11737,16 @@
     </row>
     <row r="464" spans="1:6">
       <c r="A464" t="s">
+        <v>683</v>
+      </c>
+      <c r="B464" t="s">
+        <v>684</v>
+      </c>
+      <c r="C464" t="s">
         <v>685</v>
       </c>
-      <c r="B464" t="s">
-        <v>647</v>
-      </c>
-      <c r="C464" t="s">
-        <v>683</v>
-      </c>
       <c r="D464" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E464" t="s">
         <v>686</v>
@@ -11763,10 +11763,10 @@
         <v>647</v>
       </c>
       <c r="C465" t="s">
-        <v>346</v>
+        <v>685</v>
       </c>
       <c r="D465" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E465" t="s">
         <v>688</v>
@@ -11783,10 +11783,10 @@
         <v>647</v>
       </c>
       <c r="C466" t="s">
-        <v>679</v>
+        <v>349</v>
       </c>
       <c r="D466" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E466" t="s">
         <v>690</v>
@@ -11803,10 +11803,10 @@
         <v>647</v>
       </c>
       <c r="C467" t="s">
-        <v>346</v>
+        <v>681</v>
       </c>
       <c r="D467" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E467" t="s">
         <v>692</v>
@@ -11823,10 +11823,10 @@
         <v>647</v>
       </c>
       <c r="C468" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D468" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E468" t="s">
         <v>694</v>
@@ -11843,10 +11843,10 @@
         <v>647</v>
       </c>
       <c r="C469" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D469" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E469" t="s">
         <v>696</v>
@@ -11863,10 +11863,10 @@
         <v>647</v>
       </c>
       <c r="C470" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D470" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E470" t="s">
         <v>698</v>
@@ -11883,10 +11883,10 @@
         <v>647</v>
       </c>
       <c r="C471" t="s">
-        <v>403</v>
+        <v>349</v>
       </c>
       <c r="D471" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E471" t="s">
         <v>700</v>
@@ -11903,10 +11903,10 @@
         <v>647</v>
       </c>
       <c r="C472" t="s">
-        <v>683</v>
+        <v>403</v>
       </c>
       <c r="D472" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E472" t="s">
         <v>702</v>
@@ -11923,13 +11923,13 @@
         <v>647</v>
       </c>
       <c r="C473" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="D473" t="s">
+        <v>648</v>
+      </c>
+      <c r="E473" t="s">
         <v>649</v>
-      </c>
-      <c r="E473" t="s">
-        <v>650</v>
       </c>
       <c r="F473" s="1">
         <v>46245</v>
@@ -11937,16 +11937,16 @@
     </row>
     <row r="474" spans="1:6">
       <c r="A474" t="s">
+        <v>650</v>
+      </c>
+      <c r="B474" t="s">
+        <v>647</v>
+      </c>
+      <c r="C474" t="s">
         <v>651</v>
       </c>
-      <c r="B474" t="s">
-        <v>647</v>
-      </c>
-      <c r="C474" t="s">
-        <v>648</v>
-      </c>
       <c r="D474" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E474" t="s">
         <v>652</v>
@@ -11963,10 +11963,10 @@
         <v>647</v>
       </c>
       <c r="C475" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D475" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E475" t="s">
         <v>654</v>
@@ -11983,10 +11983,10 @@
         <v>647</v>
       </c>
       <c r="C476" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D476" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E476" t="s">
         <v>656</v>
@@ -12003,10 +12003,10 @@
         <v>647</v>
       </c>
       <c r="C477" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D477" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E477" t="s">
         <v>658</v>
@@ -12023,13 +12023,13 @@
         <v>647</v>
       </c>
       <c r="C478" t="s">
+        <v>651</v>
+      </c>
+      <c r="D478" t="s">
+        <v>648</v>
+      </c>
+      <c r="E478" t="s">
         <v>660</v>
-      </c>
-      <c r="D478" t="s">
-        <v>649</v>
-      </c>
-      <c r="E478" t="s">
-        <v>661</v>
       </c>
       <c r="F478" s="1">
         <v>46245</v>
@@ -12037,16 +12037,16 @@
     </row>
     <row r="479" spans="1:6">
       <c r="A479" t="s">
+        <v>661</v>
+      </c>
+      <c r="B479" t="s">
+        <v>647</v>
+      </c>
+      <c r="C479" t="s">
         <v>662</v>
       </c>
-      <c r="B479" t="s">
-        <v>647</v>
-      </c>
-      <c r="C479" t="s">
-        <v>383</v>
-      </c>
       <c r="D479" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E479" t="s">
         <v>663</v>
@@ -12063,10 +12063,10 @@
         <v>647</v>
       </c>
       <c r="C480" t="s">
-        <v>513</v>
+        <v>383</v>
       </c>
       <c r="D480" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E480" t="s">
         <v>665</v>
@@ -12083,10 +12083,10 @@
         <v>647</v>
       </c>
       <c r="C481" t="s">
-        <v>231</v>
+        <v>513</v>
       </c>
       <c r="D481" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E481" t="s">
         <v>667</v>
@@ -12103,10 +12103,10 @@
         <v>647</v>
       </c>
       <c r="C482" t="s">
-        <v>660</v>
+        <v>228</v>
       </c>
       <c r="D482" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E482" t="s">
         <v>669</v>
@@ -12123,10 +12123,10 @@
         <v>647</v>
       </c>
       <c r="C483" t="s">
-        <v>231</v>
+        <v>662</v>
       </c>
       <c r="D483" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E483" t="s">
         <v>671</v>
@@ -12143,10 +12143,10 @@
         <v>647</v>
       </c>
       <c r="C484" t="s">
-        <v>513</v>
+        <v>228</v>
       </c>
       <c r="D484" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E484" t="s">
         <v>673</v>
@@ -12166,7 +12166,7 @@
         <v>513</v>
       </c>
       <c r="D485" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E485" t="s">
         <v>675</v>
@@ -12183,10 +12183,10 @@
         <v>647</v>
       </c>
       <c r="C486" t="s">
-        <v>660</v>
+        <v>513</v>
       </c>
       <c r="D486" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E486" t="s">
         <v>677</v>
@@ -12203,13 +12203,13 @@
         <v>647</v>
       </c>
       <c r="C487" t="s">
+        <v>662</v>
+      </c>
+      <c r="D487" t="s">
+        <v>648</v>
+      </c>
+      <c r="E487" t="s">
         <v>679</v>
-      </c>
-      <c r="D487" t="s">
-        <v>649</v>
-      </c>
-      <c r="E487" t="s">
-        <v>680</v>
       </c>
       <c r="F487" s="1">
         <v>46245</v>
@@ -12217,19 +12217,19 @@
     </row>
     <row r="488" spans="1:6">
       <c r="A488" t="s">
+        <v>680</v>
+      </c>
+      <c r="B488" t="s">
+        <v>647</v>
+      </c>
+      <c r="C488" t="s">
         <v>681</v>
       </c>
-      <c r="B488" t="s">
+      <c r="D488" t="s">
+        <v>648</v>
+      </c>
+      <c r="E488" t="s">
         <v>682</v>
-      </c>
-      <c r="C488" t="s">
-        <v>683</v>
-      </c>
-      <c r="D488" t="s">
-        <v>649</v>
-      </c>
-      <c r="E488" t="s">
-        <v>684</v>
       </c>
       <c r="F488" s="1">
         <v>46245</v>
@@ -12237,16 +12237,16 @@
     </row>
     <row r="489" spans="1:6">
       <c r="A489" t="s">
+        <v>683</v>
+      </c>
+      <c r="B489" t="s">
+        <v>684</v>
+      </c>
+      <c r="C489" t="s">
         <v>685</v>
       </c>
-      <c r="B489" t="s">
-        <v>647</v>
-      </c>
-      <c r="C489" t="s">
-        <v>683</v>
-      </c>
       <c r="D489" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E489" t="s">
         <v>686</v>
@@ -12263,10 +12263,10 @@
         <v>647</v>
       </c>
       <c r="C490" t="s">
-        <v>346</v>
+        <v>685</v>
       </c>
       <c r="D490" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E490" t="s">
         <v>688</v>
@@ -12283,10 +12283,10 @@
         <v>647</v>
       </c>
       <c r="C491" t="s">
-        <v>679</v>
+        <v>349</v>
       </c>
       <c r="D491" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E491" t="s">
         <v>690</v>
@@ -12303,10 +12303,10 @@
         <v>647</v>
       </c>
       <c r="C492" t="s">
-        <v>346</v>
+        <v>681</v>
       </c>
       <c r="D492" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E492" t="s">
         <v>692</v>
@@ -12323,10 +12323,10 @@
         <v>647</v>
       </c>
       <c r="C493" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D493" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E493" t="s">
         <v>694</v>
@@ -12343,10 +12343,10 @@
         <v>647</v>
       </c>
       <c r="C494" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D494" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E494" t="s">
         <v>696</v>
@@ -12363,10 +12363,10 @@
         <v>647</v>
       </c>
       <c r="C495" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D495" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E495" t="s">
         <v>698</v>
@@ -12383,10 +12383,10 @@
         <v>647</v>
       </c>
       <c r="C496" t="s">
-        <v>403</v>
+        <v>349</v>
       </c>
       <c r="D496" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E496" t="s">
         <v>700</v>
@@ -12403,10 +12403,10 @@
         <v>647</v>
       </c>
       <c r="C497" t="s">
-        <v>683</v>
+        <v>403</v>
       </c>
       <c r="D497" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E497" t="s">
         <v>702</v>
